--- a/data/processed/sam_auto_dashboard_2025_Q1/sam_occ_stage_major_totals_2030.xlsx
+++ b/data/processed/sam_auto_dashboard_2025_Q1/sam_occ_stage_major_totals_2030.xlsx
@@ -786,7 +786,7 @@
         <v>-9291.96318544395</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>15018.51831047981</v>
       </c>
       <c r="T2">
         <v>15511.2</v>
@@ -860,7 +860,7 @@
         <v>-231.1256430109897</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>600.5165713763025</v>
       </c>
       <c r="T3">
         <v>1641.2</v>
@@ -934,7 +934,7 @@
         <v>15.61426635281168</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>478.0402121042669</v>
       </c>
       <c r="T4">
         <v>1571.1</v>
@@ -1008,7 +1008,7 @@
         <v>686.3621687283139</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>146.4028170025125</v>
       </c>
       <c r="T5">
         <v>641.6</v>
@@ -1082,7 +1082,7 @@
         <v>496.1634413067004</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>855.2229550167954</v>
       </c>
       <c r="T6">
         <v>275.6</v>
@@ -1156,7 +1156,7 @@
         <v>157.5418263231841</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>34.49232597768779</v>
       </c>
       <c r="T7">
         <v>120.8</v>
@@ -1230,7 +1230,7 @@
         <v>4.550771639062418</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>1.45499358205347</v>
       </c>
       <c r="T8">
         <v>102.3</v>
@@ -1304,7 +1304,7 @@
         <v>57.98884522279968</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>16.01991083626585</v>
       </c>
       <c r="T9">
         <v>119.6</v>
@@ -1378,7 +1378,7 @@
         <v>24.03941256234202</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>5.084790791872785</v>
       </c>
       <c r="T10">
         <v>415</v>
@@ -1452,7 +1452,7 @@
         <v>-21.05976144930591</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>13.34128470553554</v>
       </c>
       <c r="T11">
         <v>322</v>
@@ -1526,7 +1526,7 @@
         <v>-30.93216303235124</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>57.12286646486699</v>
       </c>
       <c r="T12">
         <v>860.8</v>
@@ -1600,7 +1600,7 @@
         <v>-81.99972874849573</v>
       </c>
       <c r="S13">
-        <v>0</v>
+        <v>87.69484678134313</v>
       </c>
       <c r="T13">
         <v>1147.5</v>
@@ -1674,7 +1674,7 @@
         <v>-893.0209299352045</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>460.5561417533694</v>
       </c>
       <c r="T14">
         <v>2809.4</v>
@@ -1748,7 +1748,7 @@
         <v>-129.7486443724283</v>
       </c>
       <c r="S15">
-        <v>0</v>
+        <v>379.7721667514884</v>
       </c>
       <c r="T15">
         <v>555</v>
@@ -1822,7 +1822,7 @@
         <v>-145.3255301819718</v>
       </c>
       <c r="S16">
-        <v>0</v>
+        <v>743.0170188505629</v>
       </c>
       <c r="T16">
         <v>878.5</v>
@@ -1896,7 +1896,7 @@
         <v>-8434.44276979976</v>
       </c>
       <c r="S17">
-        <v>0</v>
+        <v>10260.31979310295</v>
       </c>
       <c r="T17">
         <v>1211.7</v>
@@ -1970,7 +1970,7 @@
         <v>-766.5687470486464</v>
       </c>
       <c r="S18">
-        <v>0</v>
+        <v>879.4596153819341</v>
       </c>
       <c r="T18">
         <v>2839.1</v>
@@ -2044,7 +2044,7 @@
         <v>-1205.343255401705</v>
       </c>
       <c r="S19">
-        <v>0</v>
+        <v>15769.25599093992</v>
       </c>
       <c r="T19">
         <v>15511.2</v>
@@ -2118,7 +2118,7 @@
         <v>211.0640106348364</v>
       </c>
       <c r="S20">
-        <v>0</v>
+        <v>630.3597676894377</v>
       </c>
       <c r="T20">
         <v>1641.2</v>
@@ -2192,7 +2192,7 @@
         <v>323.5283692110097</v>
       </c>
       <c r="S21">
-        <v>0</v>
+        <v>501.7686644224444</v>
       </c>
       <c r="T21">
         <v>1571.1</v>
@@ -2266,7 +2266,7 @@
         <v>833.3448876994462</v>
       </c>
       <c r="S22">
-        <v>0</v>
+        <v>153.556199220252</v>
       </c>
       <c r="T22">
         <v>641.6</v>
@@ -2340,7 +2340,7 @@
         <v>1246.121594854783</v>
       </c>
       <c r="S23">
-        <v>0</v>
+        <v>897.3080168993105</v>
       </c>
       <c r="T23">
         <v>275.6</v>
@@ -2414,7 +2414,7 @@
         <v>187.6432718344404</v>
       </c>
       <c r="S24">
-        <v>0</v>
+        <v>36.11025741561751</v>
       </c>
       <c r="T24">
         <v>120.8</v>
@@ -2488,7 +2488,7 @@
         <v>7.165436689632827</v>
       </c>
       <c r="S25">
-        <v>0</v>
+        <v>1.524733662651722</v>
       </c>
       <c r="T25">
         <v>102.3</v>
@@ -2562,7 +2562,7 @@
         <v>75.50369574211436</v>
       </c>
       <c r="S26">
-        <v>0</v>
+        <v>16.75922695967098</v>
       </c>
       <c r="T26">
         <v>119.6</v>
@@ -2636,7 +2636,7 @@
         <v>30.7973600223529</v>
       </c>
       <c r="S27">
-        <v>0</v>
+        <v>5.326080967002454</v>
       </c>
       <c r="T27">
         <v>415</v>
@@ -2710,7 +2710,7 @@
         <v>-15.66927661790527</v>
       </c>
       <c r="S28">
-        <v>0</v>
+        <v>14.00847267425184</v>
       </c>
       <c r="T28">
         <v>322</v>
@@ -2784,7 +2784,7 @@
         <v>-9.988041416796932</v>
       </c>
       <c r="S29">
-        <v>0</v>
+        <v>59.97601503619027</v>
       </c>
       <c r="T29">
         <v>860.8</v>
@@ -2858,7 +2858,7 @@
         <v>-22.96125103884606</v>
       </c>
       <c r="S30">
-        <v>0</v>
+        <v>92.01074676205215</v>
       </c>
       <c r="T30">
         <v>1147.5</v>
@@ -2932,7 +2932,7 @@
         <v>-636.1574262107351</v>
       </c>
       <c r="S31">
-        <v>0</v>
+        <v>483.4724530654656</v>
       </c>
       <c r="T31">
         <v>2809.4</v>
@@ -3006,7 +3006,7 @@
         <v>80.42114030541052</v>
       </c>
       <c r="S32">
-        <v>0</v>
+        <v>398.7812426965355</v>
       </c>
       <c r="T32">
         <v>555</v>
@@ -3080,7 +3080,7 @@
         <v>262.6325723146274</v>
       </c>
       <c r="S33">
-        <v>0</v>
+        <v>780.236702369919</v>
       </c>
       <c r="T33">
         <v>878.5</v>
@@ -3154,7 +3154,7 @@
         <v>-3387.151798095161</v>
       </c>
       <c r="S34">
-        <v>0</v>
+        <v>10774.53557441721</v>
       </c>
       <c r="T34">
         <v>1211.7</v>
@@ -3228,7 +3228,7 @@
         <v>-391.6378013309841</v>
       </c>
       <c r="S35">
-        <v>0</v>
+        <v>923.5218366819104</v>
       </c>
       <c r="T35">
         <v>2839.1</v>
@@ -3302,7 +3302,7 @@
         <v>4712.474579513713</v>
       </c>
       <c r="S36">
-        <v>0</v>
+        <v>16297.40128385629</v>
       </c>
       <c r="T36">
         <v>15511.2</v>
@@ -3376,7 +3376,7 @@
         <v>547.1357462321539</v>
       </c>
       <c r="S37">
-        <v>0</v>
+        <v>651.0855158557581</v>
       </c>
       <c r="T37">
         <v>1641.2</v>
@@ -3450,7 +3450,7 @@
         <v>560.4701548939884</v>
       </c>
       <c r="S38">
-        <v>0</v>
+        <v>518.2042604221215</v>
       </c>
       <c r="T38">
         <v>1571.1</v>
@@ -3524,7 +3524,7 @@
         <v>956.2346177978197</v>
       </c>
       <c r="S39">
-        <v>0</v>
+        <v>158.3352641579709</v>
       </c>
       <c r="T39">
         <v>641.6</v>
@@ -3598,7 +3598,7 @@
         <v>1853.607653411127</v>
       </c>
       <c r="S40">
-        <v>0</v>
+        <v>925.8928106377685</v>
       </c>
       <c r="T40">
         <v>275.6</v>
@@ -3672,7 +3672,7 @@
         <v>217.8319732333694</v>
       </c>
       <c r="S41">
-        <v>0</v>
+        <v>37.08525220985933</v>
       </c>
       <c r="T41">
         <v>120.8</v>
@@ -3746,7 +3746,7 @@
         <v>9.418628889684271</v>
       </c>
       <c r="S42">
-        <v>0</v>
+        <v>1.569200667867378</v>
       </c>
       <c r="T42">
         <v>102.3</v>
@@ -3820,7 +3820,7 @@
         <v>92.89135483858718</v>
       </c>
       <c r="S43">
-        <v>0</v>
+        <v>17.18489503364947</v>
       </c>
       <c r="T43">
         <v>119.6</v>
@@ -3894,7 +3894,7 @@
         <v>36.97020125331062</v>
       </c>
       <c r="S44">
-        <v>0</v>
+        <v>5.476034404345136</v>
       </c>
       <c r="T44">
         <v>415</v>
@@ -3968,7 +3968,7 @@
         <v>-11.76310690087229</v>
       </c>
       <c r="S45">
-        <v>0</v>
+        <v>14.47828754260801</v>
       </c>
       <c r="T45">
         <v>322</v>
@@ -4042,7 +4042,7 @@
         <v>5.357831395169228</v>
       </c>
       <c r="S46">
-        <v>0</v>
+        <v>61.97970948472929</v>
       </c>
       <c r="T46">
         <v>860.8</v>
@@ -4116,7 +4116,7 @@
         <v>24.37104548190928</v>
       </c>
       <c r="S47">
-        <v>0</v>
+        <v>94.94292439666387</v>
       </c>
       <c r="T47">
         <v>1147.5</v>
@@ -4190,7 +4190,7 @@
         <v>-443.9057246570701</v>
       </c>
       <c r="S48">
-        <v>0</v>
+        <v>499.4317088653771</v>
       </c>
       <c r="T48">
         <v>2809.4</v>
@@ -4264,7 +4264,7 @@
         <v>231.4790846134119</v>
       </c>
       <c r="S49">
-        <v>0</v>
+        <v>412.1929153446929</v>
       </c>
       <c r="T49">
         <v>555</v>
@@ -4338,7 +4338,7 @@
         <v>554.0999749587954</v>
       </c>
       <c r="S50">
-        <v>0</v>
+        <v>806.5408608537415</v>
       </c>
       <c r="T50">
         <v>878.5</v>
@@ -4412,7 +4412,7 @@
         <v>202.5758570484904</v>
       </c>
       <c r="S51">
-        <v>0</v>
+        <v>11138.32793403618</v>
       </c>
       <c r="T51">
         <v>1211.7</v>
@@ -4486,7 +4486,7 @@
         <v>-124.3007129761081</v>
       </c>
       <c r="S52">
-        <v>0</v>
+        <v>954.673709942959</v>
       </c>
       <c r="T52">
         <v>2839.1</v>
@@ -4560,7 +4560,7 @@
         <v>12496.39171961747</v>
       </c>
       <c r="S53">
-        <v>0</v>
+        <v>16834.91998552231</v>
       </c>
       <c r="T53">
         <v>15511.2</v>
@@ -4634,7 +4634,7 @@
         <v>1103.222715357839</v>
       </c>
       <c r="S54">
-        <v>0</v>
+        <v>672.4503425299309</v>
       </c>
       <c r="T54">
         <v>1641.2</v>
@@ -4708,7 +4708,7 @@
         <v>978.2463055856388</v>
       </c>
       <c r="S55">
-        <v>0</v>
+        <v>535.1911163062101</v>
       </c>
       <c r="T55">
         <v>1571.1</v>
@@ -4782,7 +4782,7 @@
         <v>1257.981042822454</v>
       </c>
       <c r="S56">
-        <v>0</v>
+        <v>163.4546172136582</v>
       </c>
       <c r="T56">
         <v>641.6</v>
@@ -4856,7 +4856,7 @@
         <v>3188.898601158471</v>
       </c>
       <c r="S57">
-        <v>0</v>
+        <v>956.0155886319285</v>
       </c>
       <c r="T57">
         <v>275.6</v>
@@ -4930,7 +4930,7 @@
         <v>332.1334364161485</v>
       </c>
       <c r="S58">
-        <v>0</v>
+        <v>38.24213846400049</v>
       </c>
       <c r="T58">
         <v>120.8</v>
@@ -5004,7 +5004,7 @@
         <v>15.4881526370977</v>
       </c>
       <c r="S59">
-        <v>0</v>
+        <v>1.619090547786136</v>
       </c>
       <c r="T59">
         <v>102.3</v>
@@ -5078,7 +5078,7 @@
         <v>157.5380740145688</v>
       </c>
       <c r="S60">
-        <v>0</v>
+        <v>17.71334948321139</v>
       </c>
       <c r="T60">
         <v>119.6</v>
@@ -5152,7 +5152,7 @@
         <v>56.30868078802905</v>
       </c>
       <c r="S61">
-        <v>0</v>
+        <v>5.648609304480838</v>
       </c>
       <c r="T61">
         <v>415</v>
@@ -5226,7 +5226,7 @@
         <v>-6.978082959744228</v>
       </c>
       <c r="S62">
-        <v>0</v>
+        <v>14.95598990106345</v>
       </c>
       <c r="T62">
         <v>322</v>
@@ -5300,7 +5300,7 @@
         <v>25.71546473044418</v>
       </c>
       <c r="S63">
-        <v>0</v>
+        <v>64.02249498099884</v>
       </c>
       <c r="T63">
         <v>860.8</v>
@@ -5374,7 +5374,7 @@
         <v>124.3601219438206</v>
       </c>
       <c r="S64">
-        <v>0</v>
+        <v>98.03207739659818</v>
       </c>
       <c r="T64">
         <v>1147.5</v>
@@ -5448,7 +5448,7 @@
         <v>-151.924801108451</v>
       </c>
       <c r="S65">
-        <v>0</v>
+        <v>515.8379738630854</v>
       </c>
       <c r="T65">
         <v>2809.4</v>
@@ -5522,7 +5522,7 @@
         <v>405.0785378590135</v>
       </c>
       <c r="S66">
-        <v>0</v>
+        <v>425.8035375416178</v>
       </c>
       <c r="T66">
         <v>555</v>
@@ -5596,7 +5596,7 @@
         <v>872.7796512655368</v>
       </c>
       <c r="S67">
-        <v>0</v>
+        <v>833.190811284991</v>
       </c>
       <c r="T67">
         <v>878.5</v>
@@ -5670,7 +5670,7 @@
         <v>3974.54710176737</v>
       </c>
       <c r="S68">
-        <v>0</v>
+        <v>11506.51909807324</v>
       </c>
       <c r="T68">
         <v>1211.7</v>
@@ -5744,7 +5744,7 @@
         <v>162.9967173393052</v>
       </c>
       <c r="S69">
-        <v>0</v>
+        <v>986.2231499995123</v>
       </c>
       <c r="T69">
         <v>2839.1</v>
@@ -5818,7 +5818,7 @@
         <v>14762.63872091391</v>
       </c>
       <c r="S70">
-        <v>0</v>
+        <v>16876.29735331683</v>
       </c>
       <c r="T70">
         <v>15511.2</v>
@@ -5892,7 +5892,7 @@
         <v>1347.097021009125</v>
       </c>
       <c r="S71">
-        <v>0</v>
+        <v>674.1843315510796</v>
       </c>
       <c r="T71">
         <v>1641.2</v>
@@ -5966,7 +5966,7 @@
         <v>1176.158004206409</v>
       </c>
       <c r="S72">
-        <v>0</v>
+        <v>536.5842486861462</v>
       </c>
       <c r="T72">
         <v>1571.1</v>
@@ -6040,7 +6040,7 @@
         <v>1446.541353551253</v>
       </c>
       <c r="S73">
-        <v>0</v>
+        <v>163.9328586002491</v>
       </c>
       <c r="T73">
         <v>641.6</v>
@@ -6114,7 +6114,7 @@
         <v>3963.116066406408</v>
       </c>
       <c r="S74">
-        <v>0</v>
+        <v>958.6739342165744</v>
       </c>
       <c r="T74">
         <v>275.6</v>
@@ -6188,7 +6188,7 @@
         <v>419.0297258730989</v>
       </c>
       <c r="S75">
-        <v>0</v>
+        <v>38.38541502800307</v>
       </c>
       <c r="T75">
         <v>120.8</v>
@@ -6262,7 +6262,7 @@
         <v>19.4877439589215</v>
       </c>
       <c r="S76">
-        <v>0</v>
+        <v>1.624457502198994</v>
       </c>
       <c r="T76">
         <v>102.3</v>
@@ -6336,7 +6336,7 @@
         <v>206.3885393377032</v>
       </c>
       <c r="S77">
-        <v>0</v>
+        <v>17.78540196456814</v>
       </c>
       <c r="T77">
         <v>119.6</v>
@@ -6410,7 +6410,7 @@
         <v>70.00334750062223</v>
       </c>
       <c r="S78">
-        <v>0</v>
+        <v>5.668469462515298</v>
       </c>
       <c r="T78">
         <v>415</v>
@@ -6484,7 +6484,7 @@
         <v>-5.838615099804457</v>
       </c>
       <c r="S79">
-        <v>0</v>
+        <v>14.99261422652838</v>
       </c>
       <c r="T79">
         <v>322</v>
@@ -6558,7 +6558,7 @@
         <v>31.76659195134471</v>
       </c>
       <c r="S80">
-        <v>0</v>
+        <v>64.18090836895863</v>
       </c>
       <c r="T80">
         <v>860.8</v>
@@ -6632,7 +6632,7 @@
         <v>180.5928378612543</v>
       </c>
       <c r="S81">
-        <v>0</v>
+        <v>98.30444539500621</v>
       </c>
       <c r="T81">
         <v>1147.5</v>
@@ -6706,7 +6706,7 @@
         <v>-38.80689001107385</v>
       </c>
       <c r="S82">
-        <v>0</v>
+        <v>517.1548542487518</v>
       </c>
       <c r="T82">
         <v>2809.4</v>
@@ -6780,7 +6780,7 @@
         <v>437.5845140645743</v>
       </c>
       <c r="S83">
-        <v>0</v>
+        <v>426.8383887066323</v>
       </c>
       <c r="T83">
         <v>555</v>
@@ -6854,7 +6854,7 @@
         <v>919.0564244610177</v>
       </c>
       <c r="S84">
-        <v>0</v>
+        <v>835.2024058179061</v>
       </c>
       <c r="T84">
         <v>878.5</v>
@@ -6928,7 +6928,7 @@
         <v>4390.068572578763</v>
       </c>
       <c r="S85">
-        <v>0</v>
+        <v>11534.18400675103</v>
       </c>
       <c r="T85">
         <v>1211.7</v>
@@ -7002,7 +7002,7 @@
         <v>200.3934832642717</v>
       </c>
       <c r="S86">
-        <v>0</v>
+        <v>988.6006127906782</v>
       </c>
       <c r="T86">
         <v>2839.1</v>
@@ -7076,7 +7076,7 @@
         <v>620.8072789741855</v>
       </c>
       <c r="S87">
-        <v>0</v>
+        <v>25601.96369671233</v>
       </c>
       <c r="T87">
         <v>21598.1</v>
@@ -7150,7 +7150,7 @@
         <v>239.4996551849945</v>
       </c>
       <c r="S88">
-        <v>0</v>
+        <v>1261.227636488305</v>
       </c>
       <c r="T88">
         <v>2001.9</v>
@@ -7224,7 +7224,7 @@
         <v>282.0698190718049</v>
       </c>
       <c r="S89">
-        <v>0</v>
+        <v>808.0770014781817</v>
       </c>
       <c r="T89">
         <v>1687.7</v>
@@ -7298,7 +7298,7 @@
         <v>30.54775607786564</v>
       </c>
       <c r="S90">
-        <v>0</v>
+        <v>106.3779940008147</v>
       </c>
       <c r="T90">
         <v>485.9</v>
@@ -7372,7 +7372,7 @@
         <v>338.4450765739839</v>
       </c>
       <c r="S91">
-        <v>0</v>
+        <v>372.6873957673757</v>
       </c>
       <c r="T91">
         <v>91.2</v>
@@ -7446,7 +7446,7 @@
         <v>16.33079013876835</v>
       </c>
       <c r="S92">
-        <v>0</v>
+        <v>23.80339121061118</v>
       </c>
       <c r="T92">
         <v>29.8</v>
@@ -7520,7 +7520,7 @@
         <v>0.8822756051393412</v>
       </c>
       <c r="S93">
-        <v>0</v>
+        <v>9.890552521322016</v>
       </c>
       <c r="T93">
         <v>40.9</v>
@@ -7594,7 +7594,7 @@
         <v>5.826042302169867</v>
       </c>
       <c r="S94">
-        <v>0</v>
+        <v>14.57374089409502</v>
       </c>
       <c r="T94">
         <v>35.2</v>
@@ -7668,7 +7668,7 @@
         <v>-151.5451096869128</v>
       </c>
       <c r="S95">
-        <v>0</v>
+        <v>371.7988466387791</v>
       </c>
       <c r="T95">
         <v>1236.2</v>
@@ -7742,7 +7742,7 @@
         <v>1.831663954867281</v>
       </c>
       <c r="S96">
-        <v>0</v>
+        <v>95.90375155649261</v>
       </c>
       <c r="T96">
         <v>1212.1</v>
@@ -7816,7 +7816,7 @@
         <v>-1498.834319614165</v>
       </c>
       <c r="S97">
-        <v>0</v>
+        <v>7446.875667712325</v>
       </c>
       <c r="T97">
         <v>3407.7</v>
@@ -7890,7 +7890,7 @@
         <v>-859.3516567924598</v>
       </c>
       <c r="S98">
-        <v>0</v>
+        <v>2281.113934085164</v>
       </c>
       <c r="T98">
         <v>4295.5</v>
@@ -7964,7 +7964,7 @@
         <v>12.66003272175647</v>
       </c>
       <c r="S99">
-        <v>0</v>
+        <v>57.45736515546082</v>
       </c>
       <c r="T99">
         <v>619.5000000000001</v>
@@ -8038,7 +8038,7 @@
         <v>1155.858422523816</v>
       </c>
       <c r="S100">
-        <v>0</v>
+        <v>3875.640408418882</v>
       </c>
       <c r="T100">
         <v>1057.8</v>
@@ -8112,7 +8112,7 @@
         <v>95.26757068303232</v>
       </c>
       <c r="S101">
-        <v>0</v>
+        <v>885.6204634325287</v>
       </c>
       <c r="T101">
         <v>922.0000000000001</v>
@@ -8186,7 +8186,7 @@
         <v>951.3192602295603</v>
       </c>
       <c r="S102">
-        <v>0</v>
+        <v>7990.915547351988</v>
       </c>
       <c r="T102">
         <v>4474.700000000001</v>
@@ -8260,7 +8260,7 @@
         <v>-1308.527902397997</v>
       </c>
       <c r="S103">
-        <v>0</v>
+        <v>25388.80173795375</v>
       </c>
       <c r="T103">
         <v>21598.1</v>
@@ -8334,7 +8334,7 @@
         <v>103.505221791007</v>
       </c>
       <c r="S104">
-        <v>0</v>
+        <v>1250.472166466584</v>
       </c>
       <c r="T104">
         <v>2001.9</v>
@@ -8408,7 +8408,7 @@
         <v>219.535099687866</v>
       </c>
       <c r="S105">
-        <v>0</v>
+        <v>802.8423683412055</v>
       </c>
       <c r="T105">
         <v>1687.7</v>
@@ -8482,7 +8482,7 @@
         <v>15.78277561125014</v>
       </c>
       <c r="S106">
-        <v>0</v>
+        <v>105.4964313675838</v>
       </c>
       <c r="T106">
         <v>485.9</v>
@@ -8556,7 +8556,7 @@
         <v>285.0839266518678</v>
       </c>
       <c r="S107">
-        <v>0</v>
+        <v>369.2910116105801</v>
       </c>
       <c r="T107">
         <v>91.2</v>
@@ -8630,7 +8630,7 @@
         <v>16.32823713226003</v>
       </c>
       <c r="S108">
-        <v>0</v>
+        <v>23.80311978858497</v>
       </c>
       <c r="T108">
         <v>29.8</v>
@@ -8704,7 +8704,7 @@
         <v>-0.5603941485210697</v>
       </c>
       <c r="S109">
-        <v>0</v>
+        <v>9.77444158873196</v>
       </c>
       <c r="T109">
         <v>40.9</v>
@@ -8778,7 +8778,7 @@
         <v>3.845761173169734</v>
       </c>
       <c r="S110">
-        <v>0</v>
+        <v>14.41640218373997</v>
       </c>
       <c r="T110">
         <v>35.2</v>
@@ -8852,7 +8852,7 @@
         <v>-167.2428133449519</v>
       </c>
       <c r="S111">
-        <v>0</v>
+        <v>368.4105600302697</v>
       </c>
       <c r="T111">
         <v>1236.2</v>
@@ -8926,7 +8926,7 @@
         <v>-5.236539665495798</v>
       </c>
       <c r="S112">
-        <v>0</v>
+        <v>94.90588510958034</v>
       </c>
       <c r="T112">
         <v>1212.1</v>
@@ -9000,7 +9000,7 @@
         <v>-2082.829687064674</v>
       </c>
       <c r="S113">
-        <v>0</v>
+        <v>7369.774398293126</v>
       </c>
       <c r="T113">
         <v>3407.7</v>
@@ -9074,7 +9074,7 @@
         <v>-1041.11205768909</v>
       </c>
       <c r="S114">
-        <v>0</v>
+        <v>2261.40634381644</v>
       </c>
       <c r="T114">
         <v>4295.5</v>
@@ -9148,7 +9148,7 @@
         <v>10.13620622221322</v>
       </c>
       <c r="S115">
-        <v>0</v>
+        <v>57.23968090448756</v>
       </c>
       <c r="T115">
         <v>619.5000000000001</v>
@@ -9222,7 +9222,7 @@
         <v>647.4799694203248</v>
       </c>
       <c r="S116">
-        <v>0</v>
+        <v>3830.307546732652</v>
       </c>
       <c r="T116">
         <v>1057.8</v>
@@ -9296,7 +9296,7 @@
         <v>9.337695011763572</v>
       </c>
       <c r="S117">
-        <v>0</v>
+        <v>876.9936886337796</v>
       </c>
       <c r="T117">
         <v>922.0000000000001</v>
@@ -9370,7 +9370,7 @@
         <v>677.418696813038</v>
       </c>
       <c r="S118">
-        <v>0</v>
+        <v>7953.667693086403</v>
       </c>
       <c r="T118">
         <v>4474.700000000001</v>
@@ -9444,7 +9444,7 @@
         <v>-1001.801583717723</v>
       </c>
       <c r="S119">
-        <v>0</v>
+        <v>25460.30364416917</v>
       </c>
       <c r="T119">
         <v>21598.1</v>
@@ -9518,7 +9518,7 @@
         <v>202.6440934474467</v>
       </c>
       <c r="S120">
-        <v>0</v>
+        <v>1257.693556887307</v>
       </c>
       <c r="T120">
         <v>2001.9</v>
@@ -9592,7 +9592,7 @@
         <v>158.7192565845144</v>
       </c>
       <c r="S121">
-        <v>0</v>
+        <v>795.9522870959507</v>
       </c>
       <c r="T121">
         <v>1687.7</v>
@@ -9666,7 +9666,7 @@
         <v>38.35555045598403</v>
       </c>
       <c r="S122">
-        <v>0</v>
+        <v>106.8980356949095</v>
       </c>
       <c r="T122">
         <v>485.9</v>
@@ -9740,7 +9740,7 @@
         <v>431.0922260503266</v>
       </c>
       <c r="S123">
-        <v>0</v>
+        <v>378.5842947493689</v>
       </c>
       <c r="T123">
         <v>91.2</v>
@@ -9814,7 +9814,7 @@
         <v>2.343846980640848</v>
       </c>
       <c r="S124">
-        <v>0</v>
+        <v>22.31637406429581</v>
       </c>
       <c r="T124">
         <v>29.8</v>
@@ -9888,7 +9888,7 @@
         <v>2.787137367526228</v>
       </c>
       <c r="S125">
-        <v>0</v>
+        <v>10.03685880558628</v>
       </c>
       <c r="T125">
         <v>40.9</v>
@@ -9962,7 +9962,7 @@
         <v>8.637039849127234</v>
       </c>
       <c r="S126">
-        <v>0</v>
+        <v>14.79471676891123</v>
       </c>
       <c r="T126">
         <v>35.2</v>
@@ -10036,7 +10036,7 @@
         <v>-124.2903091557334</v>
       </c>
       <c r="S127">
-        <v>0</v>
+        <v>377.681686426629</v>
       </c>
       <c r="T127">
         <v>1236.2</v>
@@ -10110,7 +10110,7 @@
         <v>3.03707035309958</v>
       </c>
       <c r="S128">
-        <v>0</v>
+        <v>96.06332696162391</v>
       </c>
       <c r="T128">
         <v>1212.1</v>
@@ -10184,7 +10184,7 @@
         <v>-696.400947581802</v>
       </c>
       <c r="S129">
-        <v>0</v>
+        <v>7555.520186759503</v>
       </c>
       <c r="T129">
         <v>3407.7</v>
@@ -10258,7 +10258,7 @@
         <v>-1042.764572690547</v>
       </c>
       <c r="S130">
-        <v>0</v>
+        <v>2265.564570960775</v>
       </c>
       <c r="T130">
         <v>4295.5</v>
@@ -10332,7 +10332,7 @@
         <v>-7.660689283574015</v>
       </c>
       <c r="S131">
-        <v>0</v>
+        <v>55.73483101503372</v>
       </c>
       <c r="T131">
         <v>619.5000000000001</v>
@@ -10406,7 +10406,7 @@
         <v>1504.297638259653</v>
       </c>
       <c r="S132">
-        <v>0</v>
+        <v>3908.985044553199</v>
       </c>
       <c r="T132">
         <v>1057.8</v>
@@ -10480,7 +10480,7 @@
         <v>232.1578065324611</v>
       </c>
       <c r="S133">
-        <v>0</v>
+        <v>899.4152762074403</v>
       </c>
       <c r="T133">
         <v>922.0000000000001</v>
@@ -10554,7 +10554,7 @@
         <v>-1714.756730886831</v>
       </c>
       <c r="S134">
-        <v>0</v>
+        <v>7715.062597218631</v>
       </c>
       <c r="T134">
         <v>4474.700000000001</v>
@@ -10628,7 +10628,7 @@
         <v>-3372.451574020437</v>
       </c>
       <c r="S135">
-        <v>0</v>
+        <v>25206.76018298394</v>
       </c>
       <c r="T135">
         <v>21598.1</v>
@@ -10702,7 +10702,7 @@
         <v>52.66939618689685</v>
       </c>
       <c r="S136">
-        <v>0</v>
+        <v>1245.694196389309</v>
       </c>
       <c r="T136">
         <v>2001.9</v>
@@ -10776,7 +10776,7 @@
         <v>61.59727461981856</v>
       </c>
       <c r="S137">
-        <v>0</v>
+        <v>787.355434193309</v>
       </c>
       <c r="T137">
         <v>1687.7</v>
@@ -10850,7 +10850,7 @@
         <v>23.9562229335429</v>
       </c>
       <c r="S138">
-        <v>0</v>
+        <v>106.0486041886265</v>
       </c>
       <c r="T138">
         <v>485.9</v>
@@ -10924,7 +10924,7 @@
         <v>393.4045390207129</v>
       </c>
       <c r="S139">
-        <v>0</v>
+        <v>376.1855109277969</v>
       </c>
       <c r="T139">
         <v>91.2</v>
@@ -10998,7 +10998,7 @@
         <v>-1.198203326612287</v>
       </c>
       <c r="S140">
-        <v>0</v>
+        <v>21.93980218004271</v>
       </c>
       <c r="T140">
         <v>29.8</v>
@@ -11072,7 +11072,7 @@
         <v>1.796326235222708</v>
       </c>
       <c r="S141">
-        <v>0</v>
+        <v>9.957443140264088</v>
       </c>
       <c r="T141">
         <v>40.9</v>
@@ -11146,7 +11146,7 @@
         <v>7.267805111051587</v>
       </c>
       <c r="S142">
-        <v>0</v>
+        <v>14.68603819360112</v>
       </c>
       <c r="T142">
         <v>35.2</v>
@@ -11220,7 +11220,7 @@
         <v>-135.3772168294115</v>
       </c>
       <c r="S143">
-        <v>0</v>
+        <v>375.2886217071746</v>
       </c>
       <c r="T143">
         <v>1236.2</v>
@@ -11294,7 +11294,7 @@
         <v>-3.545204096026509</v>
       </c>
       <c r="S144">
-        <v>0</v>
+        <v>95.13253931595113</v>
       </c>
       <c r="T144">
         <v>1212.1</v>
@@ -11368,7 +11368,7 @@
         <v>-1112.199675623699</v>
       </c>
       <c r="S145">
-        <v>0</v>
+        <v>7500.973934076121</v>
       </c>
       <c r="T145">
         <v>3407.7</v>
@@ -11442,7 +11442,7 @@
         <v>-1270.013794798018</v>
       </c>
       <c r="S146">
-        <v>0</v>
+        <v>2242.058415654637</v>
       </c>
       <c r="T146">
         <v>4295.5</v>
@@ -11516,7 +11516,7 @@
         <v>-15.69373776646364</v>
       </c>
       <c r="S147">
-        <v>0</v>
+        <v>55.0495990958137</v>
       </c>
       <c r="T147">
         <v>619.5000000000001</v>
@@ -11590,7 +11590,7 @@
         <v>1104.344514549433</v>
       </c>
       <c r="S148">
-        <v>0</v>
+        <v>3873.587434784652</v>
       </c>
       <c r="T148">
         <v>1057.8</v>
@@ -11664,7 +11664,7 @@
         <v>172.0441314309828</v>
       </c>
       <c r="S149">
-        <v>0</v>
+        <v>893.3778373688855</v>
       </c>
       <c r="T149">
         <v>922.0000000000001</v>
@@ -11738,7 +11738,7 @@
         <v>-2651.503951667837</v>
       </c>
       <c r="S150">
-        <v>0</v>
+        <v>7609.424771767754</v>
       </c>
       <c r="T150">
         <v>4474.700000000001</v>
@@ -11812,7 +11812,7 @@
         <v>1682.378589472646</v>
       </c>
       <c r="S151">
-        <v>0</v>
+        <v>25764.91114586878</v>
       </c>
       <c r="T151">
         <v>21598.1</v>
@@ -11886,7 +11886,7 @@
         <v>409.3476130045747</v>
       </c>
       <c r="S152">
-        <v>0</v>
+        <v>1273.910806269961</v>
       </c>
       <c r="T152">
         <v>2001.9</v>
@@ -11960,7 +11960,7 @@
         <v>260.8062149785237</v>
       </c>
       <c r="S153">
-        <v>0</v>
+        <v>804.5554660712664</v>
       </c>
       <c r="T153">
         <v>1687.7</v>
@@ -12034,7 +12034,7 @@
         <v>68.31102639712299</v>
       </c>
       <c r="S154">
-        <v>0</v>
+        <v>108.7094309049152</v>
       </c>
       <c r="T154">
         <v>485.9</v>
@@ -12108,7 +12108,7 @@
         <v>553.1183990791606</v>
       </c>
       <c r="S155">
-        <v>0</v>
+        <v>386.3511393806116</v>
       </c>
       <c r="T155">
         <v>91.2</v>
@@ -12182,7 +12182,7 @@
         <v>2.189954398233851</v>
       </c>
       <c r="S156">
-        <v>0</v>
+        <v>22.30001302628036</v>
       </c>
       <c r="T156">
         <v>29.8</v>
@@ -12256,7 +12256,7 @@
         <v>4.877540548622321</v>
       </c>
       <c r="S157">
-        <v>0</v>
+        <v>10.19099187112402</v>
       </c>
       <c r="T157">
         <v>40.9</v>
@@ -12330,7 +12330,7 @@
         <v>11.90189042675553</v>
       </c>
       <c r="S158">
-        <v>0</v>
+        <v>15.04935226805896</v>
       </c>
       <c r="T158">
         <v>35.2</v>
@@ -12404,7 +12404,7 @@
         <v>-88.39283120544474</v>
       </c>
       <c r="S159">
-        <v>0</v>
+        <v>385.4300136003258</v>
       </c>
       <c r="T159">
         <v>1236.2</v>
@@ -12478,7 +12478,7 @@
         <v>10.99131512321094</v>
       </c>
       <c r="S160">
-        <v>0</v>
+        <v>97.1784186792509</v>
       </c>
       <c r="T160">
         <v>1212.1</v>
@@ -12552,7 +12552,7 @@
         <v>301.4387823363286</v>
       </c>
       <c r="S161">
-        <v>0</v>
+        <v>7689.528726302257</v>
       </c>
       <c r="T161">
         <v>3407.7</v>
@@ -12626,7 +12626,7 @@
         <v>-815.7357210851405</v>
       </c>
       <c r="S162">
-        <v>0</v>
+        <v>2289.988687547905</v>
       </c>
       <c r="T162">
         <v>4295.5</v>
@@ -12700,7 +12700,7 @@
         <v>-2.171222640041151</v>
       </c>
       <c r="S163">
-        <v>0</v>
+        <v>56.20865102328318</v>
       </c>
       <c r="T163">
         <v>619.5000000000001</v>
@@ -12774,7 +12774,7 @@
         <v>2030.984977022104</v>
       </c>
       <c r="S164">
-        <v>0</v>
+        <v>3958.037522964195</v>
       </c>
       <c r="T164">
         <v>1057.8</v>
@@ -12848,7 +12848,7 @@
         <v>403.8741562432569</v>
       </c>
       <c r="S165">
-        <v>0</v>
+        <v>916.7591211563665</v>
       </c>
       <c r="T165">
         <v>922.0000000000001</v>
@@ -12922,7 +12922,7 @@
         <v>-1469.163505154604</v>
       </c>
       <c r="S166">
-        <v>0</v>
+        <v>7750.712804802981</v>
       </c>
       <c r="T166">
         <v>4474.700000000001</v>
@@ -12996,7 +12996,7 @@
         <v>-1378.270480804116</v>
       </c>
       <c r="S167">
-        <v>0</v>
+        <v>5315.956833378623</v>
       </c>
       <c r="T167">
         <v>29773.4</v>
@@ -13070,7 +13070,7 @@
         <v>150.7631783594588</v>
       </c>
       <c r="S168">
-        <v>0</v>
+        <v>303.9821101075269</v>
       </c>
       <c r="T168">
         <v>3480</v>
@@ -13144,7 +13144,7 @@
         <v>228.3865853353145</v>
       </c>
       <c r="S169">
-        <v>0</v>
+        <v>239.8506219508269</v>
       </c>
       <c r="T169">
         <v>3317.5</v>
@@ -13218,7 +13218,7 @@
         <v>6.377286871504111</v>
       </c>
       <c r="S170">
-        <v>0</v>
+        <v>42.08559040889504</v>
       </c>
       <c r="T170">
         <v>922.5</v>
@@ -13292,7 +13292,7 @@
         <v>638.6794065889226</v>
       </c>
       <c r="S171">
-        <v>0</v>
+        <v>295.6403240819541</v>
       </c>
       <c r="T171">
         <v>438.9</v>
@@ -13366,7 +13366,7 @@
         <v>33.13503966316239</v>
       </c>
       <c r="S172">
-        <v>0</v>
+        <v>37.36658020812551</v>
       </c>
       <c r="T172">
         <v>103.5</v>
@@ -13440,7 +13440,7 @@
         <v>-0.8585333063813891</v>
       </c>
       <c r="S173">
-        <v>0</v>
+        <v>5.457034952495015</v>
       </c>
       <c r="T173">
         <v>34</v>
@@ -13514,7 +13514,7 @@
         <v>-0.09998854351387365</v>
       </c>
       <c r="S174">
-        <v>0</v>
+        <v>2.967649339202517</v>
       </c>
       <c r="T174">
         <v>161</v>
@@ -13588,7 +13588,7 @@
         <v>4.152086295496247</v>
       </c>
       <c r="S175">
-        <v>0</v>
+        <v>38.88664633039156</v>
       </c>
       <c r="T175">
         <v>1756.5</v>
@@ -13662,7 +13662,7 @@
         <v>-71.46357648931098</v>
       </c>
       <c r="S176">
-        <v>0</v>
+        <v>121.6950710864035</v>
       </c>
       <c r="T176">
         <v>1534.8</v>
@@ -13736,7 +13736,7 @@
         <v>-755.7725692129789</v>
       </c>
       <c r="S177">
-        <v>0</v>
+        <v>404.7035850924045</v>
       </c>
       <c r="T177">
         <v>6865</v>
@@ -13810,7 +13810,7 @@
         <v>1.081477835678925</v>
       </c>
       <c r="S178">
-        <v>0</v>
+        <v>25.99875403007505</v>
       </c>
       <c r="T178">
         <v>405</v>
@@ -13884,7 +13884,7 @@
         <v>471.7285735596433</v>
       </c>
       <c r="S179">
-        <v>0</v>
+        <v>254.4733036820572</v>
       </c>
       <c r="T179">
         <v>1352.6</v>
@@ -13958,7 +13958,7 @@
         <v>-2106.821493852127</v>
       </c>
       <c r="S180">
-        <v>0</v>
+        <v>3141.425383705909</v>
       </c>
       <c r="T180">
         <v>2950.1</v>
@@ -14032,7 +14032,7 @@
         <v>22.44204609100052</v>
       </c>
       <c r="S181">
-        <v>0</v>
+        <v>401.4241784023552</v>
       </c>
       <c r="T181">
         <v>6452</v>
@@ -14106,7 +14106,7 @@
         <v>-2770.39516564089</v>
       </c>
       <c r="S182">
-        <v>0</v>
+        <v>5274.556372905497</v>
       </c>
       <c r="T182">
         <v>29773.4</v>
@@ -14180,7 +14180,7 @@
         <v>46.32931660856048</v>
       </c>
       <c r="S183">
-        <v>0</v>
+        <v>301.2292371045923</v>
       </c>
       <c r="T183">
         <v>3480</v>
@@ -14254,7 +14254,7 @@
         <v>146.8488980497532</v>
       </c>
       <c r="S184">
-        <v>0</v>
+        <v>237.1354523425619</v>
       </c>
       <c r="T184">
         <v>3317.5</v>
@@ -14328,7 +14328,7 @@
         <v>-20.01715086739523</v>
       </c>
       <c r="S185">
-        <v>0</v>
+        <v>41.39885804386468</v>
       </c>
       <c r="T185">
         <v>922.5</v>
@@ -14402,7 +14402,7 @@
         <v>518.6292849584534</v>
       </c>
       <c r="S186">
-        <v>0</v>
+        <v>292.2402021528736</v>
       </c>
       <c r="T186">
         <v>438.9</v>
@@ -14476,7 +14476,7 @@
         <v>10.90157012544955</v>
       </c>
       <c r="S187">
-        <v>0</v>
+        <v>36.77198267915738</v>
       </c>
       <c r="T187">
         <v>103.5</v>
@@ -14550,7 +14550,7 @@
         <v>-3.43554087891647</v>
       </c>
       <c r="S188">
-        <v>0</v>
+        <v>5.36012673859669</v>
       </c>
       <c r="T188">
         <v>34</v>
@@ -14624,7 +14624,7 @@
         <v>-1.782357908829141</v>
       </c>
       <c r="S189">
-        <v>0</v>
+        <v>2.90002884441645</v>
       </c>
       <c r="T189">
         <v>161</v>
@@ -14698,7 +14698,7 @@
         <v>-2.68722089635196</v>
       </c>
       <c r="S190">
-        <v>0</v>
+        <v>38.58250114341939</v>
       </c>
       <c r="T190">
         <v>1756.5</v>
@@ -14772,7 +14772,7 @@
         <v>-111.233784582495</v>
       </c>
       <c r="S191">
-        <v>0</v>
+        <v>120.2341212250436</v>
       </c>
       <c r="T191">
         <v>1534.8</v>
@@ -14846,7 +14846,7 @@
         <v>-866.5739264293679</v>
       </c>
       <c r="S192">
-        <v>0</v>
+        <v>400.9969529497591</v>
       </c>
       <c r="T192">
         <v>6865</v>
@@ -14920,7 +14920,7 @@
         <v>-5.044621553400248</v>
       </c>
       <c r="S193">
-        <v>0</v>
+        <v>25.7710847912718</v>
       </c>
       <c r="T193">
         <v>405</v>
@@ -14994,7 +14994,7 @@
         <v>408.750004421152</v>
       </c>
       <c r="S194">
-        <v>0</v>
+        <v>253.0152662365293</v>
       </c>
       <c r="T194">
         <v>1352.6</v>
@@ -15068,7 +15068,7 @@
         <v>-2803.539286973479</v>
       </c>
       <c r="S195">
-        <v>0</v>
+        <v>3120.98139808511</v>
       </c>
       <c r="T195">
         <v>2950.1</v>
@@ -15142,7 +15142,7 @@
         <v>-87.54034971402689</v>
       </c>
       <c r="S196">
-        <v>0</v>
+        <v>397.9391605682997</v>
       </c>
       <c r="T196">
         <v>6452</v>
@@ -15216,7 +15216,7 @@
         <v>-9759.961319345806</v>
       </c>
       <c r="S197">
-        <v>0</v>
+        <v>5035.087363301524</v>
       </c>
       <c r="T197">
         <v>29773.4</v>
@@ -15290,7 +15290,7 @@
         <v>-447.5626826627358</v>
       </c>
       <c r="S198">
-        <v>0</v>
+        <v>288.5531740923974</v>
       </c>
       <c r="T198">
         <v>3480</v>
@@ -15364,7 +15364,7 @@
         <v>-187.9540665994573</v>
       </c>
       <c r="S199">
-        <v>0</v>
+        <v>228.1639889156295</v>
       </c>
       <c r="T199">
         <v>3317.5</v>
@@ -15438,7 +15438,7 @@
         <v>-99.17202096735127</v>
       </c>
       <c r="S200">
-        <v>0</v>
+        <v>39.99505801837205</v>
       </c>
       <c r="T200">
         <v>922.5</v>
@@ -15512,7 +15512,7 @@
         <v>-4.578404129126284</v>
       </c>
       <c r="S201">
-        <v>0</v>
+        <v>281.7041630318628</v>
       </c>
       <c r="T201">
         <v>438.9</v>
@@ -15586,7 +15586,7 @@
         <v>-40.90062982682616</v>
       </c>
       <c r="S202">
-        <v>0</v>
+        <v>34.99945865032051</v>
       </c>
       <c r="T202">
         <v>103.5</v>
@@ -15660,7 +15660,7 @@
         <v>-12.73676355191725</v>
       </c>
       <c r="S203">
-        <v>0</v>
+        <v>5.209714305783457</v>
       </c>
       <c r="T203">
         <v>34</v>
@@ -15734,7 +15734,7 @@
         <v>-4.893206062411522</v>
       </c>
       <c r="S204">
-        <v>0</v>
+        <v>2.766095468520514</v>
       </c>
       <c r="T204">
         <v>161</v>
@@ -15808,7 +15808,7 @@
         <v>-39.04511665018902</v>
       </c>
       <c r="S205">
-        <v>0</v>
+        <v>36.79110788413499</v>
       </c>
       <c r="T205">
         <v>1756.5</v>
@@ -15882,7 +15882,7 @@
         <v>-276.9138805005596</v>
       </c>
       <c r="S206">
-        <v>0</v>
+        <v>115.9928862790839</v>
       </c>
       <c r="T206">
         <v>1534.8</v>
@@ -15956,7 +15956,7 @@
         <v>-1372.709516322993</v>
       </c>
       <c r="S207">
-        <v>0</v>
+        <v>384.1478161959105</v>
       </c>
       <c r="T207">
         <v>6865</v>
@@ -16030,7 +16030,7 @@
         <v>-41.3913059525413</v>
       </c>
       <c r="S208">
-        <v>0</v>
+        <v>24.66003989160621</v>
       </c>
       <c r="T208">
         <v>405</v>
@@ -16104,7 +16104,7 @@
         <v>51.90999104166804</v>
       </c>
       <c r="S209">
-        <v>0</v>
+        <v>239.6630187376871</v>
       </c>
       <c r="T209">
         <v>1352.6</v>
@@ -16178,7 +16178,7 @@
         <v>-6765.583141395284</v>
       </c>
       <c r="S210">
-        <v>0</v>
+        <v>2974.4649353042</v>
       </c>
       <c r="T210">
         <v>2950.1</v>
@@ -16252,7 +16252,7 @@
         <v>-518.4305757661059</v>
       </c>
       <c r="S211">
-        <v>0</v>
+        <v>377.9759065260152</v>
       </c>
       <c r="T211">
         <v>6452</v>
@@ -16326,7 +16326,7 @@
         <v>-7383.458640111465</v>
       </c>
       <c r="S212">
-        <v>0</v>
+        <v>5090.010723792841</v>
       </c>
       <c r="T212">
         <v>29773.4</v>
@@ -16400,7 +16400,7 @@
         <v>-274.803145377</v>
       </c>
       <c r="S213">
-        <v>0</v>
+        <v>291.5742179430147</v>
       </c>
       <c r="T213">
         <v>3480</v>
@@ -16474,7 +16474,7 @@
         <v>-63.32739388951268</v>
       </c>
       <c r="S214">
-        <v>0</v>
+        <v>230.5230116284792</v>
       </c>
       <c r="T214">
         <v>3317.5</v>
@@ -16548,7 +16548,7 @@
         <v>-72.73492235971617</v>
       </c>
       <c r="S215">
-        <v>0</v>
+        <v>40.30150760354638</v>
       </c>
       <c r="T215">
         <v>922.5</v>
@@ -16622,7 +16622,7 @@
         <v>199.0741676368161</v>
       </c>
       <c r="S216">
-        <v>0</v>
+        <v>284.6003380915761</v>
       </c>
       <c r="T216">
         <v>438.9</v>
@@ -16696,7 +16696,7 @@
         <v>-25.23381756096978</v>
       </c>
       <c r="S217">
-        <v>0</v>
+        <v>35.38934356565523</v>
       </c>
       <c r="T217">
         <v>103.5</v>
@@ -16770,7 +16770,7 @@
         <v>-8.341603073931878</v>
       </c>
       <c r="S218">
-        <v>0</v>
+        <v>5.276417452312211</v>
       </c>
       <c r="T218">
         <v>34</v>
@@ -16844,7 +16844,7 @@
         <v>-3.900402799093087</v>
       </c>
       <c r="S219">
-        <v>0</v>
+        <v>2.799512334151499</v>
       </c>
       <c r="T219">
         <v>161</v>
@@ -16918,7 +16918,7 @@
         <v>-26.0444050630482</v>
       </c>
       <c r="S220">
-        <v>0</v>
+        <v>37.23242921406518</v>
       </c>
       <c r="T220">
         <v>1756.5</v>
@@ -16992,7 +16992,7 @@
         <v>-211.6322308376421</v>
       </c>
       <c r="S221">
-        <v>0</v>
+        <v>117.2217209344061</v>
       </c>
       <c r="T221">
         <v>1534.8</v>
@@ -17066,7 +17066,7 @@
         <v>-1191.285323040858</v>
       </c>
       <c r="S222">
-        <v>0</v>
+        <v>388.3815689371806</v>
       </c>
       <c r="T222">
         <v>6865</v>
@@ -17140,7 +17140,7 @@
         <v>-28.19622497566593</v>
       </c>
       <c r="S223">
-        <v>0</v>
+        <v>24.92986530850494</v>
       </c>
       <c r="T223">
         <v>405</v>
@@ -17214,7 +17214,7 @@
         <v>160.3604351454469</v>
       </c>
       <c r="S224">
-        <v>0</v>
+        <v>242.3056845985553</v>
       </c>
       <c r="T224">
         <v>1352.6</v>
@@ -17288,7 +17288,7 @@
         <v>-5449.812032132264</v>
       </c>
       <c r="S225">
-        <v>0</v>
+        <v>3007.347968650809</v>
       </c>
       <c r="T225">
         <v>2950.1</v>
@@ -17362,7 +17362,7 @@
         <v>-387.5817417839826</v>
       </c>
       <c r="S226">
-        <v>0</v>
+        <v>382.1271375305843</v>
       </c>
       <c r="T226">
         <v>6452</v>
@@ -17436,7 +17436,7 @@
         <v>-8104.458601648425</v>
       </c>
       <c r="S227">
-        <v>0</v>
+        <v>5105.596727577089</v>
       </c>
       <c r="T227">
         <v>29773.4</v>
@@ -17510,7 +17510,7 @@
         <v>-352.8407142217493</v>
       </c>
       <c r="S228">
-        <v>0</v>
+        <v>291.7301549557659</v>
       </c>
       <c r="T228">
         <v>3480</v>
@@ -17584,7 +17584,7 @@
         <v>-135.2308046915259</v>
       </c>
       <c r="S229">
-        <v>0</v>
+        <v>230.1592484135503</v>
       </c>
       <c r="T229">
         <v>3317.5</v>
@@ -17658,7 +17658,7 @@
         <v>-89.70561287246028</v>
       </c>
       <c r="S230">
-        <v>0</v>
+        <v>40.1212656134609</v>
       </c>
       <c r="T230">
         <v>922.5</v>
@@ -17732,7 +17732,7 @@
         <v>46.09897836057462</v>
       </c>
       <c r="S231">
-        <v>0</v>
+        <v>283.6635146651244</v>
       </c>
       <c r="T231">
         <v>438.9</v>
@@ -17806,7 +17806,7 @@
         <v>-14.97811351890118</v>
       </c>
       <c r="S232">
-        <v>0</v>
+        <v>35.76644933115316</v>
       </c>
       <c r="T232">
         <v>103.5</v>
@@ -17880,7 +17880,7 @@
         <v>-12.26479426136973</v>
       </c>
       <c r="S233">
-        <v>0</v>
+        <v>5.243795697544872</v>
       </c>
       <c r="T233">
         <v>34</v>
@@ -17954,7 +17954,7 @@
         <v>-3.022196437465652</v>
       </c>
       <c r="S234">
-        <v>0</v>
+        <v>2.838102970662694</v>
       </c>
       <c r="T234">
         <v>161</v>
@@ -18028,7 +18028,7 @@
         <v>-30.24626201584908</v>
       </c>
       <c r="S235">
-        <v>0</v>
+        <v>37.38006730658338</v>
       </c>
       <c r="T235">
         <v>1756.5</v>
@@ -18102,7 +18102,7 @@
         <v>-258.5799117676797</v>
       </c>
       <c r="S236">
-        <v>0</v>
+        <v>116.8289057149108</v>
       </c>
       <c r="T236">
         <v>1534.8</v>
@@ -18176,7 +18176,7 @@
         <v>-1261.426192992987</v>
       </c>
       <c r="S237">
-        <v>0</v>
+        <v>388.8552580607735</v>
       </c>
       <c r="T237">
         <v>6865</v>
@@ -18250,7 +18250,7 @@
         <v>-36.53979471721709</v>
       </c>
       <c r="S238">
-        <v>0</v>
+        <v>24.92608866445978</v>
       </c>
       <c r="T238">
         <v>405</v>
@@ -18324,7 +18324,7 @@
         <v>160.2820257133244</v>
       </c>
       <c r="S239">
-        <v>0</v>
+        <v>244.062566550808</v>
       </c>
       <c r="T239">
         <v>1352.6</v>
@@ -18398,7 +18398,7 @@
         <v>-5758.317111905766</v>
       </c>
       <c r="S240">
-        <v>0</v>
+        <v>3018.943154414059</v>
       </c>
       <c r="T240">
         <v>2950.1</v>
@@ -18472,7 +18472,7 @@
         <v>-357.6880963193071</v>
       </c>
       <c r="S241">
-        <v>0</v>
+        <v>385.0781552182319</v>
       </c>
       <c r="T241">
         <v>6452</v>
@@ -18546,7 +18546,7 @@
         <v>-10670.23366624804</v>
       </c>
       <c r="S242">
-        <v>0</v>
+        <v>20334.47514385842</v>
       </c>
       <c r="T242">
         <v>45284.6</v>
@@ -18620,7 +18620,7 @@
         <v>-80.36246465154545</v>
       </c>
       <c r="S243">
-        <v>0</v>
+        <v>904.4986814838294</v>
       </c>
       <c r="T243">
         <v>5121.200000000001</v>
@@ -18694,7 +18694,7 @@
         <v>244.0008516881171</v>
       </c>
       <c r="S244">
-        <v>0</v>
+        <v>717.8908340550938</v>
       </c>
       <c r="T244">
         <v>4888.6</v>
@@ -18768,7 +18768,7 @@
         <v>692.7394555998162</v>
       </c>
       <c r="S245">
-        <v>0</v>
+        <v>188.4884074114076</v>
       </c>
       <c r="T245">
         <v>1564.1</v>
@@ -18842,7 +18842,7 @@
         <v>1134.842847895619</v>
       </c>
       <c r="S246">
-        <v>0</v>
+        <v>1150.86327909875</v>
       </c>
       <c r="T246">
         <v>714.5000000000001</v>
@@ -18916,7 +18916,7 @@
         <v>190.6768659863455</v>
       </c>
       <c r="S247">
-        <v>0</v>
+        <v>71.8589061858133</v>
       </c>
       <c r="T247">
         <v>224.3</v>
@@ -18990,7 +18990,7 @@
         <v>4.550771639062418</v>
       </c>
       <c r="S248">
-        <v>0</v>
+        <v>1.45499358205347</v>
       </c>
       <c r="T248">
         <v>102.3</v>
@@ -19064,7 +19064,7 @@
         <v>57.13031191641767</v>
       </c>
       <c r="S249">
-        <v>0</v>
+        <v>21.47694578876087</v>
       </c>
       <c r="T249">
         <v>153.6</v>
@@ -19138,7 +19138,7 @@
         <v>24.03941256234202</v>
       </c>
       <c r="S250">
-        <v>0</v>
+        <v>5.084790791872785</v>
       </c>
       <c r="T250">
         <v>415</v>
@@ -19212,7 +19212,7 @@
         <v>-21.15974999281977</v>
       </c>
       <c r="S251">
-        <v>0</v>
+        <v>16.30893404473806</v>
       </c>
       <c r="T251">
         <v>483</v>
@@ -19286,7 +19286,7 @@
         <v>-26.78007673685488</v>
       </c>
       <c r="S252">
-        <v>0</v>
+        <v>96.00951279525854</v>
       </c>
       <c r="T252">
         <v>2617.3</v>
@@ -19360,7 +19360,7 @@
         <v>-153.4633052378067</v>
       </c>
       <c r="S253">
-        <v>0</v>
+        <v>209.3899178677466</v>
       </c>
       <c r="T253">
         <v>2682.3</v>
@@ -19434,7 +19434,7 @@
         <v>-1648.793499148178</v>
       </c>
       <c r="S254">
-        <v>0</v>
+        <v>865.2597268457739</v>
       </c>
       <c r="T254">
         <v>9674.400000000001</v>
@@ -19508,7 +19508,7 @@
         <v>-128.6671665367494</v>
       </c>
       <c r="S255">
-        <v>0</v>
+        <v>405.7709207815635</v>
       </c>
       <c r="T255">
         <v>960</v>
@@ -19582,7 +19582,7 @@
         <v>326.4030433776752</v>
       </c>
       <c r="S256">
-        <v>0</v>
+        <v>997.49032253262</v>
       </c>
       <c r="T256">
         <v>2231.1</v>
@@ -19656,7 +19656,7 @@
         <v>-10541.26426365189</v>
       </c>
       <c r="S257">
-        <v>0</v>
+        <v>13401.74517680886</v>
       </c>
       <c r="T257">
         <v>4161.800000000001</v>
@@ -19730,7 +19730,7 @@
         <v>-744.1267009576477</v>
       </c>
       <c r="S258">
-        <v>0</v>
+        <v>1280.883793784289</v>
       </c>
       <c r="T258">
         <v>9291.099999999999</v>
@@ -19804,7 +19804,7 @@
         <v>-3975.738421042566</v>
       </c>
       <c r="S259">
-        <v>0</v>
+        <v>21043.81236384542</v>
       </c>
       <c r="T259">
         <v>45284.6</v>
@@ -19878,7 +19878,7 @@
         <v>257.3933272433933</v>
       </c>
       <c r="S260">
-        <v>0</v>
+        <v>931.5890047940298</v>
       </c>
       <c r="T260">
         <v>5121.200000000001</v>
@@ -19952,7 +19952,7 @@
         <v>470.3772672607593</v>
       </c>
       <c r="S261">
-        <v>0</v>
+        <v>738.9041167650062</v>
       </c>
       <c r="T261">
         <v>4888.6</v>
@@ -20026,7 +20026,7 @@
         <v>813.3277368320505</v>
       </c>
       <c r="S262">
-        <v>0</v>
+        <v>194.9550572641166</v>
       </c>
       <c r="T262">
         <v>1564.1</v>
@@ -20100,7 +20100,7 @@
         <v>1764.750879813233</v>
       </c>
       <c r="S263">
-        <v>0</v>
+        <v>1189.548219052184</v>
       </c>
       <c r="T263">
         <v>714.5000000000001</v>
@@ -20174,7 +20174,7 @@
         <v>198.5448419598897</v>
       </c>
       <c r="S264">
-        <v>0</v>
+        <v>72.8822400947749</v>
       </c>
       <c r="T264">
         <v>224.3</v>
@@ -20248,7 +20248,7 @@
         <v>7.165436689632827</v>
       </c>
       <c r="S265">
-        <v>0</v>
+        <v>1.524733662651722</v>
       </c>
       <c r="T265">
         <v>102.3</v>
@@ -20322,7 +20322,7 @@
         <v>72.06815486319738</v>
       </c>
       <c r="S266">
-        <v>0</v>
+        <v>22.11935369826767</v>
       </c>
       <c r="T266">
         <v>153.6</v>
@@ -20396,7 +20396,7 @@
         <v>30.7973600223529</v>
       </c>
       <c r="S267">
-        <v>0</v>
+        <v>5.326080967002454</v>
       </c>
       <c r="T267">
         <v>415</v>
@@ -20470,7 +20470,7 @@
         <v>-17.45163452673441</v>
       </c>
       <c r="S268">
-        <v>0</v>
+        <v>16.9085015186683</v>
       </c>
       <c r="T268">
         <v>483</v>
@@ -20544,7 +20544,7 @@
         <v>-12.67526231314923</v>
       </c>
       <c r="S269">
-        <v>0</v>
+        <v>98.55851617960967</v>
       </c>
       <c r="T269">
         <v>2617.3</v>
@@ -20618,7 +20618,7 @@
         <v>-134.195035621342</v>
       </c>
       <c r="S270">
-        <v>0</v>
+        <v>212.2448679870957</v>
       </c>
       <c r="T270">
         <v>2682.3</v>
@@ -20692,7 +20692,7 @@
         <v>-1502.731352640105</v>
       </c>
       <c r="S271">
-        <v>0</v>
+        <v>884.4694060152246</v>
       </c>
       <c r="T271">
         <v>9674.400000000001</v>
@@ -20766,7 +20766,7 @@
         <v>75.37651875201118</v>
       </c>
       <c r="S272">
-        <v>0</v>
+        <v>424.5523274878072</v>
       </c>
       <c r="T272">
         <v>960</v>
@@ -20840,7 +20840,7 @@
         <v>671.3825767357812</v>
       </c>
       <c r="S273">
-        <v>0</v>
+        <v>1033.251968606449</v>
       </c>
       <c r="T273">
         <v>2231.1</v>
@@ -20914,7 +20914,7 @@
         <v>-6190.691085068625</v>
       </c>
       <c r="S274">
-        <v>0</v>
+        <v>13895.51697250232</v>
       </c>
       <c r="T274">
         <v>4161.800000000001</v>
@@ -20988,7 +20988,7 @@
         <v>-479.1781510450128</v>
       </c>
       <c r="S275">
-        <v>0</v>
+        <v>1321.46099725021</v>
       </c>
       <c r="T275">
         <v>9291.099999999999</v>
@@ -21062,7 +21062,7 @@
         <v>-5047.486739831918</v>
       </c>
       <c r="S276">
-        <v>0</v>
+        <v>21332.48864715781</v>
       </c>
       <c r="T276">
         <v>45284.6</v>
@@ -21136,7 +21136,7 @@
         <v>99.57306356941262</v>
       </c>
       <c r="S277">
-        <v>0</v>
+        <v>939.6386899481555</v>
       </c>
       <c r="T277">
         <v>5121.200000000001</v>
@@ -21210,7 +21210,7 @@
         <v>372.5160882945238</v>
       </c>
       <c r="S278">
-        <v>0</v>
+        <v>746.3682493377511</v>
       </c>
       <c r="T278">
         <v>4888.6</v>
@@ -21284,7 +21284,7 @@
         <v>857.0625968304648</v>
       </c>
       <c r="S279">
-        <v>0</v>
+        <v>198.3303221763429</v>
       </c>
       <c r="T279">
         <v>1564.1</v>
@@ -21358,7 +21358,7 @@
         <v>1849.029249282015</v>
       </c>
       <c r="S280">
-        <v>0</v>
+        <v>1207.596973669632</v>
       </c>
       <c r="T280">
         <v>714.5000000000001</v>
@@ -21432,7 +21432,7 @@
         <v>176.9313434065425</v>
       </c>
       <c r="S281">
-        <v>0</v>
+        <v>72.08471086017983</v>
       </c>
       <c r="T281">
         <v>224.3</v>
@@ -21506,7 +21506,7 @@
         <v>9.418628889684271</v>
       </c>
       <c r="S282">
-        <v>0</v>
+        <v>1.569200667867378</v>
       </c>
       <c r="T282">
         <v>102.3</v>
@@ -21580,7 +21580,7 @@
         <v>80.15459128666953</v>
       </c>
       <c r="S283">
-        <v>0</v>
+        <v>22.39460933943293</v>
       </c>
       <c r="T283">
         <v>153.6</v>
@@ -21654,7 +21654,7 @@
         <v>36.97020125331062</v>
       </c>
       <c r="S284">
-        <v>0</v>
+        <v>5.476034404345136</v>
       </c>
       <c r="T284">
         <v>415</v>
@@ -21728,7 +21728,7 @@
         <v>-16.65631296328377</v>
       </c>
       <c r="S285">
-        <v>0</v>
+        <v>17.24438301112852</v>
       </c>
       <c r="T285">
         <v>483</v>
@@ -21802,7 +21802,7 @@
         <v>-33.68728525502002</v>
       </c>
       <c r="S286">
-        <v>0</v>
+        <v>98.77081736886429</v>
       </c>
       <c r="T286">
         <v>2617.3</v>
@@ -21876,7 +21876,7 @@
         <v>-252.5428350186521</v>
       </c>
       <c r="S287">
-        <v>0</v>
+        <v>210.9358106757479</v>
       </c>
       <c r="T287">
         <v>2682.3</v>
@@ -21950,7 +21950,7 @@
         <v>-1816.615240980063</v>
       </c>
       <c r="S288">
-        <v>0</v>
+        <v>883.5795250612875</v>
       </c>
       <c r="T288">
         <v>9674.400000000001</v>
@@ -22024,7 +22024,7 @@
         <v>190.0877786608708</v>
       </c>
       <c r="S289">
-        <v>0</v>
+        <v>436.8529552362992</v>
       </c>
       <c r="T289">
         <v>960</v>
@@ -22098,7 +22098,7 @@
         <v>606.0099660004635</v>
       </c>
       <c r="S290">
-        <v>0</v>
+        <v>1046.203879591428</v>
       </c>
       <c r="T290">
         <v>2231.1</v>
@@ -22172,7 +22172,7 @@
         <v>-6563.007284346793</v>
       </c>
       <c r="S291">
-        <v>0</v>
+        <v>14112.79286934038</v>
       </c>
       <c r="T291">
         <v>4161.800000000001</v>
@@ -22246,7 +22246,7 @@
         <v>-642.7312887422158</v>
       </c>
       <c r="S292">
-        <v>0</v>
+        <v>1332.649616468974</v>
       </c>
       <c r="T292">
         <v>9291.099999999999</v>
@@ -22320,7 +22320,7 @@
         <v>5112.933079506096</v>
       </c>
       <c r="S293">
-        <v>0</v>
+        <v>21924.93070931515</v>
       </c>
       <c r="T293">
         <v>45284.6</v>
@@ -22394,7 +22394,7 @@
         <v>828.4195699808261</v>
       </c>
       <c r="S294">
-        <v>0</v>
+        <v>964.0245604729455</v>
       </c>
       <c r="T294">
         <v>5121.200000000001</v>
@@ -22468,7 +22468,7 @@
         <v>914.9189116961243</v>
       </c>
       <c r="S295">
-        <v>0</v>
+        <v>765.7141279346894</v>
       </c>
       <c r="T295">
         <v>4888.6</v>
@@ -22542,7 +22542,7 @@
         <v>1185.246120462734</v>
       </c>
       <c r="S296">
-        <v>0</v>
+        <v>203.7561248172045</v>
       </c>
       <c r="T296">
         <v>1564.1</v>
@@ -22616,7 +22616,7 @@
         <v>3387.972768795269</v>
       </c>
       <c r="S297">
-        <v>0</v>
+        <v>1240.615926723505</v>
       </c>
       <c r="T297">
         <v>714.5000000000001</v>
@@ -22690,7 +22690,7 @@
         <v>306.8996188551791</v>
       </c>
       <c r="S298">
-        <v>0</v>
+        <v>73.63148202965571</v>
       </c>
       <c r="T298">
         <v>224.3</v>
@@ -22764,7 +22764,7 @@
         <v>15.4881526370977</v>
       </c>
       <c r="S299">
-        <v>0</v>
+        <v>1.619090547786136</v>
       </c>
       <c r="T299">
         <v>102.3</v>
@@ -22838,7 +22838,7 @@
         <v>149.1964709406366</v>
       </c>
       <c r="S300">
-        <v>0</v>
+        <v>22.9897669355236</v>
       </c>
       <c r="T300">
         <v>153.6</v>
@@ -22912,7 +22912,7 @@
         <v>56.30868078802905</v>
       </c>
       <c r="S301">
-        <v>0</v>
+        <v>5.648609304480838</v>
       </c>
       <c r="T301">
         <v>415</v>
@@ -22986,7 +22986,7 @@
         <v>-10.87848575883731</v>
       </c>
       <c r="S302">
-        <v>0</v>
+        <v>17.75550223521495</v>
       </c>
       <c r="T302">
         <v>483</v>
@@ -23060,7 +23060,7 @@
         <v>-0.3289403326041338</v>
       </c>
       <c r="S303">
-        <v>0</v>
+        <v>101.254924195064</v>
       </c>
       <c r="T303">
         <v>2617.3</v>
@@ -23134,7 +23134,7 @@
         <v>-87.2721088938215</v>
       </c>
       <c r="S304">
-        <v>0</v>
+        <v>215.2537983310042</v>
       </c>
       <c r="T304">
         <v>2682.3</v>
@@ -23208,7 +23208,7 @@
         <v>-1343.210124149307</v>
       </c>
       <c r="S305">
-        <v>0</v>
+        <v>904.219542800266</v>
       </c>
       <c r="T305">
         <v>9674.400000000001</v>
@@ -23282,7 +23282,7 @@
         <v>376.8823128833474</v>
       </c>
       <c r="S306">
-        <v>0</v>
+        <v>450.7334028501227</v>
       </c>
       <c r="T306">
         <v>960</v>
@@ -23356,7 +23356,7 @@
         <v>1033.140086410986</v>
       </c>
       <c r="S307">
-        <v>0</v>
+        <v>1075.496495883546</v>
       </c>
       <c r="T307">
         <v>2231.1</v>
@@ -23430,7 +23430,7 @@
         <v>-1475.264930364909</v>
       </c>
       <c r="S308">
-        <v>0</v>
+        <v>14513.86706672405</v>
       </c>
       <c r="T308">
         <v>4161.800000000001</v>
@@ -23504,7 +23504,7 @@
         <v>-224.5850244446847</v>
       </c>
       <c r="S309">
-        <v>0</v>
+        <v>1368.350287530096</v>
       </c>
       <c r="T309">
         <v>9291.099999999999</v>
@@ -23578,7 +23578,7 @@
         <v>6658.180119265511</v>
       </c>
       <c r="S310">
-        <v>0</v>
+        <v>21981.89408089391</v>
       </c>
       <c r="T310">
         <v>45284.6</v>
@@ -23652,7 +23652,7 @@
         <v>994.2563067873707</v>
       </c>
       <c r="S311">
-        <v>0</v>
+        <v>965.9144865068457</v>
       </c>
       <c r="T311">
         <v>5121.200000000001</v>
@@ -23726,7 +23726,7 @@
         <v>1040.927199514877</v>
       </c>
       <c r="S312">
-        <v>0</v>
+        <v>766.7434970996966</v>
       </c>
       <c r="T312">
         <v>4888.6</v>
@@ -23800,7 +23800,7 @@
         <v>1356.835740678789</v>
       </c>
       <c r="S313">
-        <v>0</v>
+        <v>204.0541242137101</v>
       </c>
       <c r="T313">
         <v>1564.1</v>
@@ -23874,7 +23874,7 @@
         <v>4009.215044766999</v>
       </c>
       <c r="S314">
-        <v>0</v>
+        <v>1242.337448881699</v>
       </c>
       <c r="T314">
         <v>714.5000000000001</v>
@@ -23948,7 +23948,7 @@
         <v>404.0516123541984</v>
       </c>
       <c r="S315">
-        <v>0</v>
+        <v>74.15186435915624</v>
       </c>
       <c r="T315">
         <v>224.3</v>
@@ -24022,7 +24022,7 @@
         <v>19.4877439589215</v>
       </c>
       <c r="S316">
-        <v>0</v>
+        <v>1.624457502198994</v>
       </c>
       <c r="T316">
         <v>102.3</v>
@@ -24096,7 +24096,7 @@
         <v>194.1237450763338</v>
       </c>
       <c r="S317">
-        <v>0</v>
+        <v>23.02919766211301</v>
       </c>
       <c r="T317">
         <v>153.6</v>
@@ -24170,7 +24170,7 @@
         <v>70.00334750062223</v>
       </c>
       <c r="S318">
-        <v>0</v>
+        <v>5.668469462515298</v>
       </c>
       <c r="T318">
         <v>415</v>
@@ -24244,7 +24244,7 @@
         <v>-8.860811537270081</v>
       </c>
       <c r="S319">
-        <v>0</v>
+        <v>17.83071719719108</v>
       </c>
       <c r="T319">
         <v>483</v>
@@ -24318,7 +24318,7 @@
         <v>1.520329935495738</v>
       </c>
       <c r="S320">
-        <v>0</v>
+        <v>101.560975675542</v>
       </c>
       <c r="T320">
         <v>2617.3</v>
@@ -24392,7 +24392,7 @@
         <v>-77.98707390642812</v>
       </c>
       <c r="S321">
-        <v>0</v>
+        <v>215.1333511099171</v>
       </c>
       <c r="T321">
         <v>2682.3</v>
@@ -24466,7 +24466,7 @@
         <v>-1300.233083004059</v>
       </c>
       <c r="S322">
-        <v>0</v>
+        <v>906.0101123095253</v>
       </c>
       <c r="T322">
         <v>9674.400000000001</v>
@@ -24540,7 +24540,7 @@
         <v>401.0447193473583</v>
       </c>
       <c r="S323">
-        <v>0</v>
+        <v>451.7644773710921</v>
       </c>
       <c r="T323">
         <v>960</v>
@@ -24614,7 +24614,7 @@
         <v>1079.338450174342</v>
       </c>
       <c r="S324">
-        <v>0</v>
+        <v>1079.264972368714</v>
       </c>
       <c r="T324">
         <v>2231.1</v>
@@ -24688,7 +24688,7 @@
         <v>-1368.248539327033</v>
       </c>
       <c r="S325">
-        <v>0</v>
+        <v>14553.12716116509</v>
       </c>
       <c r="T325">
         <v>4161.800000000001</v>
@@ -24762,7 +24762,7 @@
         <v>-157.2946130550372</v>
       </c>
       <c r="S326">
-        <v>0</v>
+        <v>1373.67876800891</v>
       </c>
       <c r="T326">
         <v>9291.099999999999</v>

--- a/data/processed/sam_auto_dashboard_2025_Q1/sam_occ_stage_major_totals_2030.xlsx
+++ b/data/processed/sam_auto_dashboard_2025_Q1/sam_occ_stage_major_totals_2030.xlsx
@@ -4536,16 +4536,16 @@
         <v>91</v>
       </c>
       <c r="K53">
-        <v>58468.43468090173</v>
+        <v>58465.63384705097</v>
       </c>
       <c r="L53">
-        <v>174202.5417901687</v>
+        <v>174517.3236457442</v>
       </c>
       <c r="M53">
-        <v>174202.5417901687</v>
+        <v>174517.3236457442</v>
       </c>
       <c r="N53">
-        <v>295807.3917196175</v>
+        <v>294775.9009696277</v>
       </c>
       <c r="O53">
         <v>167459.8846685799</v>
@@ -4554,13 +4554,13 @@
         <v>283311</v>
       </c>
       <c r="Q53">
-        <v>6742.657121588825</v>
+        <v>7057.438977164333</v>
       </c>
       <c r="R53">
-        <v>12496.39171961747</v>
+        <v>11464.90096962766</v>
       </c>
       <c r="S53">
-        <v>16834.91998552231</v>
+        <v>16865.60007781033</v>
       </c>
       <c r="T53">
         <v>15511.2</v>
@@ -4569,10 +4569,10 @@
         <v>283880</v>
       </c>
       <c r="V53">
-        <v>0.04026431246464326</v>
+        <v>0.04214405731337819</v>
       </c>
       <c r="W53">
-        <v>0.04410838873046748</v>
+        <v>0.04046754615820657</v>
       </c>
       <c r="X53">
         <v>2030</v>
@@ -4610,16 +4610,16 @@
         <v>92</v>
       </c>
       <c r="K54">
-        <v>133644.4938713617</v>
+        <v>133642.4349942972</v>
       </c>
       <c r="L54">
-        <v>9088.78746034164</v>
+        <v>9104.290623861782</v>
       </c>
       <c r="M54">
-        <v>9088.78746034164</v>
+        <v>9104.290623861782</v>
       </c>
       <c r="N54">
-        <v>23695.29250639926</v>
+        <v>23549.08881679662</v>
       </c>
       <c r="O54">
         <v>8710.64045604184</v>
@@ -4628,13 +4628,13 @@
         <v>22592.06979104142</v>
       </c>
       <c r="Q54">
-        <v>378.1470042998008</v>
+        <v>393.650167819942</v>
       </c>
       <c r="R54">
-        <v>1103.222715357839</v>
+        <v>957.0190257551949</v>
       </c>
       <c r="S54">
-        <v>672.4503425299309</v>
+        <v>673.5964397286272</v>
       </c>
       <c r="T54">
         <v>1641.2</v>
@@ -4643,10 +4643,10 @@
         <v>22000</v>
       </c>
       <c r="V54">
-        <v>0.04341207815982256</v>
+        <v>0.04519187421481734</v>
       </c>
       <c r="W54">
-        <v>0.04883229936706847</v>
+        <v>0.04236083876363943</v>
       </c>
       <c r="X54">
         <v>2030</v>
@@ -4684,16 +4684,16 @@
         <v>92</v>
       </c>
       <c r="K55">
-        <v>82766.47043756278</v>
+        <v>82765.57712757097</v>
       </c>
       <c r="L55">
-        <v>6226.562339582109</v>
+        <v>6236.957415641142</v>
       </c>
       <c r="M55">
-        <v>6226.562339582109</v>
+        <v>6236.957415641142</v>
       </c>
       <c r="N55">
-        <v>18261.13927845244</v>
+        <v>18138.30100681383</v>
       </c>
       <c r="O55">
         <v>5838.94851770782</v>
@@ -4702,13 +4702,13 @@
         <v>17282.8929728668</v>
       </c>
       <c r="Q55">
-        <v>387.6138218742899</v>
+        <v>398.0088979333223</v>
       </c>
       <c r="R55">
-        <v>978.2463055856388</v>
+        <v>855.4080339470311</v>
       </c>
       <c r="S55">
-        <v>535.1911163062101</v>
+        <v>536.0904888541069</v>
       </c>
       <c r="T55">
         <v>1571.1</v>
@@ -4717,10 +4717,10 @@
         <v>17290</v>
       </c>
       <c r="V55">
-        <v>0.0663841821346379</v>
+        <v>0.06816448145180214</v>
       </c>
       <c r="W55">
-        <v>0.05660199985739843</v>
+        <v>0.04949449350233061</v>
       </c>
       <c r="X55">
         <v>2030</v>
@@ -4758,16 +4758,16 @@
         <v>92</v>
       </c>
       <c r="K56">
-        <v>118077.9910343914</v>
+        <v>118076.7253110608</v>
       </c>
       <c r="L56">
-        <v>2629.560677592864</v>
+        <v>2633.181781509002</v>
       </c>
       <c r="M56">
-        <v>2629.560677592864</v>
+        <v>2633.181781509002</v>
       </c>
       <c r="N56">
-        <v>14615.47777724053</v>
+        <v>14486.4042406617</v>
       </c>
       <c r="O56">
         <v>2440.576037062486</v>
@@ -4776,13 +4776,13 @@
         <v>13357.49673441807</v>
       </c>
       <c r="Q56">
-        <v>188.9846405303783</v>
+        <v>192.6057444465159</v>
       </c>
       <c r="R56">
-        <v>1257.981042822454</v>
+        <v>1128.907506243624</v>
       </c>
       <c r="S56">
-        <v>163.4546172136582</v>
+        <v>163.6777324012541</v>
       </c>
       <c r="T56">
         <v>641.6</v>
@@ -4791,10 +4791,10 @@
         <v>9290</v>
       </c>
       <c r="V56">
-        <v>0.07743444074696526</v>
+        <v>0.0789181494539048</v>
       </c>
       <c r="W56">
-        <v>0.09417790382692229</v>
+        <v>0.08451490041055254</v>
       </c>
       <c r="X56">
         <v>2030</v>
@@ -4832,16 +4832,16 @@
         <v>92</v>
       </c>
       <c r="K57">
-        <v>96315.96009981638</v>
+        <v>96315.3109600024</v>
       </c>
       <c r="L57">
-        <v>14101.27270505088</v>
+        <v>14122.42669813223</v>
       </c>
       <c r="M57">
-        <v>14101.27270505088</v>
+        <v>14122.42669813223</v>
       </c>
       <c r="N57">
-        <v>62794.49970229457</v>
+        <v>62276.57686068555</v>
       </c>
       <c r="O57">
         <v>13246.33269150341</v>
@@ -4850,13 +4850,13 @@
         <v>59605.6011011361</v>
       </c>
       <c r="Q57">
-        <v>854.9400135474662</v>
+        <v>876.0940066288204</v>
       </c>
       <c r="R57">
-        <v>3188.898601158471</v>
+        <v>2670.975759549452</v>
       </c>
       <c r="S57">
-        <v>956.0155886319285</v>
+        <v>957.4562044310694</v>
       </c>
       <c r="T57">
         <v>275.6</v>
@@ -4865,10 +4865,10 @@
         <v>63380</v>
       </c>
       <c r="V57">
-        <v>0.06454163831290828</v>
+        <v>0.0661386080987361</v>
       </c>
       <c r="W57">
-        <v>0.05349998225414574</v>
+        <v>0.04481081828228627</v>
       </c>
       <c r="X57">
         <v>2030</v>
@@ -4906,16 +4906,16 @@
         <v>92</v>
       </c>
       <c r="K58">
-        <v>80998.85822265956</v>
+        <v>80988.77521416682</v>
       </c>
       <c r="L58">
-        <v>362.6764123895715</v>
+        <v>362.7298870714664</v>
       </c>
       <c r="M58">
-        <v>362.6764123895715</v>
+        <v>362.7298870714664</v>
       </c>
       <c r="N58">
-        <v>6019.960070067721</v>
+        <v>5957.382440688689</v>
       </c>
       <c r="O58">
         <v>351.7110858924985</v>
@@ -4924,13 +4924,13 @@
         <v>5687.826633651573</v>
       </c>
       <c r="Q58">
-        <v>10.96532649707302</v>
+        <v>11.01880117896792</v>
       </c>
       <c r="R58">
-        <v>332.1334364161485</v>
+        <v>269.5558070371162</v>
       </c>
       <c r="S58">
-        <v>38.24213846400049</v>
+        <v>38.26366315894489</v>
       </c>
       <c r="T58">
         <v>120.8</v>
@@ -4939,10 +4939,10 @@
         <v>5450</v>
       </c>
       <c r="V58">
-        <v>0.03117708521824816</v>
+        <v>0.0313291267206057</v>
       </c>
       <c r="W58">
-        <v>0.05839373416396124</v>
+        <v>0.04739170590086392</v>
       </c>
       <c r="X58">
         <v>2030</v>
@@ -4980,16 +4980,16 @@
         <v>92</v>
       </c>
       <c r="K59">
-        <v>150162.5117650926</v>
+        <v>150174.8380548663</v>
       </c>
       <c r="L59">
-        <v>44.42671534225047</v>
+        <v>44.48193364951828</v>
       </c>
       <c r="M59">
-        <v>44.42671534225047</v>
+        <v>44.48193364951828</v>
       </c>
       <c r="N59">
-        <v>300.4492600726056</v>
+        <v>297.6700837107662</v>
       </c>
       <c r="O59">
         <v>40.27150559824349</v>
@@ -4998,13 +4998,13 @@
         <v>284.9611074355079</v>
       </c>
       <c r="Q59">
-        <v>4.155209744006989</v>
+        <v>4.210428051274789</v>
       </c>
       <c r="R59">
-        <v>15.4881526370977</v>
+        <v>12.70897627525829</v>
       </c>
       <c r="S59">
-        <v>1.619090547786136</v>
+        <v>1.620685099736256</v>
       </c>
       <c r="T59">
         <v>102.3</v>
@@ -5013,10 +5013,10 @@
         <v>240</v>
       </c>
       <c r="V59">
-        <v>0.103179895618013</v>
+        <v>0.1045510464217269</v>
       </c>
       <c r="W59">
-        <v>0.05435181234548984</v>
+        <v>0.04459898541815772</v>
       </c>
       <c r="X59">
         <v>2030</v>
@@ -5054,16 +5054,16 @@
         <v>92</v>
       </c>
       <c r="K60">
-        <v>76815.07491678887</v>
+        <v>76820.60714429966</v>
       </c>
       <c r="L60">
-        <v>217.2593170009278</v>
+        <v>217.3148190416842</v>
       </c>
       <c r="M60">
-        <v>217.2593170009278</v>
+        <v>217.3148190416842</v>
       </c>
       <c r="N60">
-        <v>3395.507574127575</v>
+        <v>3360.377073597399</v>
       </c>
       <c r="O60">
         <v>198.1717542114366</v>
@@ -5072,13 +5072,13 @@
         <v>3237.969500113006</v>
       </c>
       <c r="Q60">
-        <v>19.08756278949124</v>
+        <v>19.14306483024762</v>
       </c>
       <c r="R60">
-        <v>157.5380740145688</v>
+        <v>122.4075734843927</v>
       </c>
       <c r="S60">
-        <v>17.71334948321139</v>
+        <v>17.71775996862934</v>
       </c>
       <c r="T60">
         <v>119.6</v>
@@ -5087,10 +5087,10 @@
         <v>3990</v>
       </c>
       <c r="V60">
-        <v>0.09631828140919636</v>
+        <v>0.0965983518005457</v>
       </c>
       <c r="W60">
-        <v>0.04865335328485049</v>
+        <v>0.03780380682403608</v>
       </c>
       <c r="X60">
         <v>2030</v>
@@ -5128,16 +5128,16 @@
         <v>92</v>
       </c>
       <c r="K61">
-        <v>91530.91698707784</v>
+        <v>91555.83560616118</v>
       </c>
       <c r="L61">
-        <v>102.5990446473618</v>
+        <v>102.6939150718847</v>
       </c>
       <c r="M61">
-        <v>102.5990446473618</v>
+        <v>102.6939150718847</v>
       </c>
       <c r="N61">
-        <v>987.0204820224494</v>
+        <v>977.324029538358</v>
       </c>
       <c r="O61">
         <v>93.12047186834673</v>
@@ -5146,13 +5146,13 @@
         <v>930.7118012344204</v>
       </c>
       <c r="Q61">
-        <v>9.478572779015053</v>
+        <v>9.573443203538019</v>
       </c>
       <c r="R61">
-        <v>56.30868078802905</v>
+        <v>46.61222830393763</v>
       </c>
       <c r="S61">
-        <v>5.648609304480838</v>
+        <v>5.653061856090656</v>
       </c>
       <c r="T61">
         <v>415</v>
@@ -5161,10 +5161,10 @@
         <v>430</v>
       </c>
       <c r="V61">
-        <v>0.1017882812322495</v>
+        <v>0.1028070735839151</v>
       </c>
       <c r="W61">
-        <v>0.06050066273291668</v>
+        <v>0.05008234368804066</v>
       </c>
       <c r="X61">
         <v>2030</v>
@@ -5202,16 +5202,16 @@
         <v>91</v>
       </c>
       <c r="K62">
-        <v>38370</v>
+        <v>38369.99999999999</v>
       </c>
       <c r="L62">
-        <v>117.4741914837568</v>
+        <v>117.6893133889625</v>
       </c>
       <c r="M62">
-        <v>117.4741914837568</v>
+        <v>117.6893133889625</v>
       </c>
       <c r="N62">
-        <v>173.9120474811299</v>
+        <v>173.5023526994174</v>
       </c>
       <c r="O62">
         <v>124.4232992476619</v>
@@ -5220,13 +5220,13 @@
         <v>180.8901304408741</v>
       </c>
       <c r="Q62">
-        <v>-6.949107763905189</v>
+        <v>-6.733985858699455</v>
       </c>
       <c r="R62">
-        <v>-6.978082959744228</v>
+        <v>-7.387777741456716</v>
       </c>
       <c r="S62">
-        <v>14.95598990106345</v>
+        <v>14.98337771281272</v>
       </c>
       <c r="T62">
         <v>322</v>
@@ -5235,10 +5235,10 @@
         <v>110</v>
       </c>
       <c r="V62">
-        <v>-0.05585053447323509</v>
+        <v>-0.0541215825284909</v>
       </c>
       <c r="W62">
-        <v>-0.0385763609254795</v>
+        <v>-0.04084124282209797</v>
       </c>
       <c r="X62">
         <v>2030</v>
@@ -5276,16 +5276,16 @@
         <v>91</v>
       </c>
       <c r="K63">
-        <v>35934.78216770893</v>
+        <v>35934.72042807692</v>
       </c>
       <c r="L63">
-        <v>450.5182913670511</v>
+        <v>451.3309792434026</v>
       </c>
       <c r="M63">
-        <v>450.5182913670511</v>
+        <v>451.3309792434026</v>
       </c>
       <c r="N63">
-        <v>777.5184845608429</v>
+        <v>774.7109927949615</v>
       </c>
       <c r="O63">
         <v>441.235448267697</v>
@@ -5294,13 +5294,13 @@
         <v>751.8030198303987</v>
       </c>
       <c r="Q63">
-        <v>9.282843099354068</v>
+        <v>10.09553097570563</v>
       </c>
       <c r="R63">
-        <v>25.71546473044418</v>
+        <v>22.90797296456276</v>
       </c>
       <c r="S63">
-        <v>64.02249498099884</v>
+        <v>64.13813702395662</v>
       </c>
       <c r="T63">
         <v>860.8</v>
@@ -5309,10 +5309,10 @@
         <v>510</v>
       </c>
       <c r="V63">
-        <v>0.02103829856780269</v>
+        <v>0.02288014486447309</v>
       </c>
       <c r="W63">
-        <v>0.03420505644716006</v>
+        <v>0.03047071155650669</v>
       </c>
       <c r="X63">
         <v>2030</v>
@@ -5350,16 +5350,16 @@
         <v>91</v>
       </c>
       <c r="K64">
-        <v>76882.26961349336</v>
+        <v>76882.91742532871</v>
       </c>
       <c r="L64">
-        <v>1127.260483588278</v>
+        <v>1128.992983990728</v>
       </c>
       <c r="M64">
-        <v>1127.260483588278</v>
+        <v>1128.992983990728</v>
       </c>
       <c r="N64">
-        <v>4647.705883033533</v>
+        <v>4610.463957634615</v>
       </c>
       <c r="O64">
         <v>1107.102473900015</v>
@@ -5368,13 +5368,13 @@
         <v>4523.345761089712</v>
       </c>
       <c r="Q64">
-        <v>20.15800968826215</v>
+        <v>21.89051009071295</v>
       </c>
       <c r="R64">
-        <v>124.3601219438206</v>
+        <v>87.11819654490318</v>
       </c>
       <c r="S64">
-        <v>98.03207739659818</v>
+        <v>98.18002140428628</v>
       </c>
       <c r="T64">
         <v>1147.5</v>
@@ -5383,10 +5383,10 @@
         <v>4280</v>
       </c>
       <c r="V64">
-        <v>0.01820789869365125</v>
+        <v>0.01977279484671256</v>
       </c>
       <c r="W64">
-        <v>0.02749295068565821</v>
+        <v>0.01925968102953856</v>
       </c>
       <c r="X64">
         <v>2030</v>
@@ -5424,16 +5424,16 @@
         <v>91</v>
       </c>
       <c r="K65">
-        <v>49432.20961463591</v>
+        <v>49432.5158459025</v>
       </c>
       <c r="L65">
-        <v>5383.556705865421</v>
+        <v>5392.969193355127</v>
       </c>
       <c r="M65">
-        <v>5383.556705865421</v>
+        <v>5392.969193355127</v>
       </c>
       <c r="N65">
-        <v>11974.73343021609</v>
+        <v>11911.17579630372</v>
       </c>
       <c r="O65">
         <v>5482.394427589174</v>
@@ -5442,13 +5442,13 @@
         <v>12126.65823132454</v>
       </c>
       <c r="Q65">
-        <v>-98.83772172375211</v>
+        <v>-89.42523423404691</v>
       </c>
       <c r="R65">
-        <v>-151.924801108451</v>
+        <v>-215.4824350208219</v>
       </c>
       <c r="S65">
-        <v>515.8379738630854</v>
+        <v>516.7301129043956</v>
       </c>
       <c r="T65">
         <v>2809.4</v>
@@ -5457,10 +5457,10 @@
         <v>11660</v>
       </c>
       <c r="V65">
-        <v>-0.0180282033752203</v>
+        <v>-0.01631134633145517</v>
       </c>
       <c r="W65">
-        <v>-0.01252816713478508</v>
+        <v>-0.01776931706248686</v>
       </c>
       <c r="X65">
         <v>2030</v>
@@ -5498,16 +5498,16 @@
         <v>91</v>
       </c>
       <c r="K66">
-        <v>62420.77022140103</v>
+        <v>62420.54997594535</v>
       </c>
       <c r="L66">
-        <v>4623.623187811296</v>
+        <v>4632.180484066939</v>
       </c>
       <c r="M66">
-        <v>4623.623187811296</v>
+        <v>4632.180484066939</v>
       </c>
       <c r="N66">
-        <v>6033.323754685109</v>
+        <v>6026.274426235133</v>
       </c>
       <c r="O66">
         <v>4254.21899112446</v>
@@ -5516,13 +5516,13 @@
         <v>5628.245216826095</v>
       </c>
       <c r="Q66">
-        <v>369.4041966868363</v>
+        <v>377.9614929424797</v>
       </c>
       <c r="R66">
-        <v>405.0785378590135</v>
+        <v>398.0292094090382</v>
       </c>
       <c r="S66">
-        <v>425.8035375416178</v>
+        <v>426.5909618259044</v>
       </c>
       <c r="T66">
         <v>555</v>
@@ -5531,10 +5531,10 @@
         <v>5700</v>
       </c>
       <c r="V66">
-        <v>0.08683243562626208</v>
+        <v>0.08884392028972123</v>
       </c>
       <c r="W66">
-        <v>0.0719724394111327</v>
+        <v>0.0707199480610933</v>
       </c>
       <c r="X66">
         <v>2030</v>
@@ -5572,16 +5572,16 @@
         <v>91</v>
       </c>
       <c r="K67">
-        <v>62597.91770173412</v>
+        <v>62598.0218235336</v>
       </c>
       <c r="L67">
-        <v>9036.123731044989</v>
+        <v>9052.973929116597</v>
       </c>
       <c r="M67">
-        <v>9036.123731044989</v>
+        <v>9052.973929116597</v>
       </c>
       <c r="N67">
-        <v>10656.72005895604</v>
+        <v>10655.62883082456</v>
       </c>
       <c r="O67">
         <v>8240.513688409237</v>
@@ -5590,13 +5590,13 @@
         <v>9783.940407690501</v>
       </c>
       <c r="Q67">
-        <v>795.6100426357516</v>
+        <v>812.4602407073598</v>
       </c>
       <c r="R67">
-        <v>872.7796512655368</v>
+        <v>871.6884231340573</v>
       </c>
       <c r="S67">
-        <v>833.190811284991</v>
+        <v>834.7446508735214</v>
       </c>
       <c r="T67">
         <v>878.5</v>
@@ -5605,10 +5605,10 @@
         <v>11230</v>
       </c>
       <c r="V67">
-        <v>0.09654859790534946</v>
+        <v>0.09859339738129827</v>
       </c>
       <c r="W67">
-        <v>0.08920533189056458</v>
+        <v>0.08909379930900656</v>
       </c>
       <c r="X67">
         <v>2030</v>
@@ -5646,16 +5646,16 @@
         <v>91</v>
       </c>
       <c r="K68">
-        <v>45782.18130735075</v>
+        <v>45782.15175628399</v>
       </c>
       <c r="L68">
-        <v>112367.5586814424</v>
+        <v>112578.2686237749</v>
       </c>
       <c r="M68">
-        <v>112367.5586814424</v>
+        <v>112578.2686237749</v>
       </c>
       <c r="N68">
-        <v>122001.9841651077</v>
+        <v>122106.0325466015</v>
       </c>
       <c r="O68">
         <v>108682.1765008627</v>
@@ -5664,13 +5664,13 @@
         <v>118027.4370633403</v>
       </c>
       <c r="Q68">
-        <v>3685.382180579792</v>
+        <v>3896.092122912247</v>
       </c>
       <c r="R68">
-        <v>3974.54710176737</v>
+        <v>4078.59548326119</v>
       </c>
       <c r="S68">
-        <v>11506.51909807324</v>
+        <v>11528.09087671714</v>
       </c>
       <c r="T68">
         <v>1211.7</v>
@@ -5679,10 +5679,10 @@
         <v>119140</v>
       </c>
       <c r="V68">
-        <v>0.03390972005930099</v>
+        <v>0.03584849189030846</v>
       </c>
       <c r="W68">
-        <v>0.03367477258388996</v>
+        <v>0.03455633355041321</v>
       </c>
       <c r="X68">
         <v>2030</v>
@@ -5720,16 +5720,16 @@
         <v>91</v>
       </c>
       <c r="K69">
-        <v>42334.97209343869</v>
+        <v>42334.97199096794</v>
       </c>
       <c r="L69">
-        <v>8323.281845617903</v>
+        <v>8338.841064828863</v>
       </c>
       <c r="M69">
-        <v>8323.281845617903</v>
+        <v>8338.841064828863</v>
       </c>
       <c r="N69">
-        <v>9472.147244899992</v>
+        <v>9474.987514040844</v>
       </c>
       <c r="O69">
         <v>8208.047319292958</v>
@@ -5738,13 +5738,13 @@
         <v>9309.150527560687</v>
       </c>
       <c r="Q69">
-        <v>115.2345263249445</v>
+        <v>130.7937455359042</v>
       </c>
       <c r="R69">
-        <v>162.9967173393052</v>
+        <v>165.8369864801571</v>
       </c>
       <c r="S69">
-        <v>986.2231499995123</v>
+        <v>988.0659038498646</v>
       </c>
       <c r="T69">
         <v>2839.1</v>
@@ -5753,10 +5753,10 @@
         <v>9180</v>
       </c>
       <c r="V69">
-        <v>0.01403921320654262</v>
+        <v>0.01593481865394153</v>
       </c>
       <c r="W69">
-        <v>0.01750930086013077</v>
+        <v>0.01781440594275276</v>
       </c>
       <c r="X69">
         <v>2030</v>
@@ -10604,16 +10604,16 @@
         <v>91</v>
       </c>
       <c r="K135">
-        <v>55007.40686937168</v>
+        <v>55018.78293544857</v>
       </c>
       <c r="L135">
-        <v>230847.5484259796</v>
+        <v>231573.8973031781</v>
       </c>
       <c r="M135">
-        <v>230847.5484259796</v>
+        <v>231573.8973031781</v>
       </c>
       <c r="N135">
-        <v>230847.5484259796</v>
+        <v>231573.8973031781</v>
       </c>
       <c r="O135">
         <v>234220</v>
@@ -10622,13 +10622,13 @@
         <v>234220</v>
       </c>
       <c r="Q135">
-        <v>-3372.451574020437</v>
+        <v>-2646.102696821879</v>
       </c>
       <c r="R135">
-        <v>-3372.451574020437</v>
+        <v>-2646.102696821879</v>
       </c>
       <c r="S135">
-        <v>25206.76018298394</v>
+        <v>25287.8573085726</v>
       </c>
       <c r="T135">
         <v>21598.1</v>
@@ -10637,10 +10637,10 @@
         <v>210150</v>
       </c>
       <c r="V135">
-        <v>-0.01439864902237399</v>
+        <v>-0.01129750959278404</v>
       </c>
       <c r="W135">
-        <v>-0.01439864902237399</v>
+        <v>-0.01129750959278404</v>
       </c>
       <c r="X135">
         <v>2030</v>
@@ -10678,16 +10678,16 @@
         <v>92</v>
       </c>
       <c r="K136">
-        <v>119198.1226800089</v>
+        <v>119207.1800988609</v>
       </c>
       <c r="L136">
-        <v>15687.84096494983</v>
+        <v>15741.25296909812</v>
       </c>
       <c r="M136">
-        <v>15687.84096494983</v>
+        <v>15741.25296909812</v>
       </c>
       <c r="N136">
-        <v>15687.84096494983</v>
+        <v>15741.25296909812</v>
       </c>
       <c r="O136">
         <v>15635.17156876293</v>
@@ -10696,13 +10696,13 @@
         <v>15635.17156876293</v>
       </c>
       <c r="Q136">
-        <v>52.66939618689685</v>
+        <v>106.0814003351916</v>
       </c>
       <c r="R136">
-        <v>52.66939618689685</v>
+        <v>106.0814003351916</v>
       </c>
       <c r="S136">
-        <v>1245.694196389309</v>
+        <v>1249.905527925696</v>
       </c>
       <c r="T136">
         <v>2001.9</v>
@@ -10711,10 +10711,10 @@
         <v>12340</v>
       </c>
       <c r="V136">
-        <v>0.003368648431854982</v>
+        <v>0.00678479285428045</v>
       </c>
       <c r="W136">
-        <v>0.003368648431854982</v>
+        <v>0.00678479285428045</v>
       </c>
       <c r="X136">
         <v>2030</v>
@@ -10752,16 +10752,16 @@
         <v>92</v>
       </c>
       <c r="K137">
-        <v>80458.68897856526</v>
+        <v>80462.14633964593</v>
       </c>
       <c r="L137">
-        <v>9058.023119765116</v>
+        <v>9095.391228399572</v>
       </c>
       <c r="M137">
-        <v>9058.023119765116</v>
+        <v>9095.391228399572</v>
       </c>
       <c r="N137">
-        <v>9058.023119765116</v>
+        <v>9095.391228399572</v>
       </c>
       <c r="O137">
         <v>8996.425845145297</v>
@@ -10770,13 +10770,13 @@
         <v>8996.425845145297</v>
       </c>
       <c r="Q137">
-        <v>61.59727461981856</v>
+        <v>98.96538325427537</v>
       </c>
       <c r="R137">
-        <v>61.59727461981856</v>
+        <v>98.96538325427537</v>
       </c>
       <c r="S137">
-        <v>787.355434193309</v>
+        <v>790.6687437137296</v>
       </c>
       <c r="T137">
         <v>1687.7</v>
@@ -10785,10 +10785,10 @@
         <v>5430</v>
       </c>
       <c r="V137">
-        <v>0.006846860706694763</v>
+        <v>0.01100052231383418</v>
       </c>
       <c r="W137">
-        <v>0.006846860706694763</v>
+        <v>0.01100052231383418</v>
       </c>
       <c r="X137">
         <v>2030</v>
@@ -10826,16 +10826,16 @@
         <v>92</v>
       </c>
       <c r="K138">
-        <v>101324.1162124164</v>
+        <v>101344.6550157526</v>
       </c>
       <c r="L138">
-        <v>1776.952150773552</v>
+        <v>1785.561126347123</v>
       </c>
       <c r="M138">
-        <v>1776.952150773552</v>
+        <v>1785.561126347123</v>
       </c>
       <c r="N138">
-        <v>1776.952150773552</v>
+        <v>1785.561126347123</v>
       </c>
       <c r="O138">
         <v>1752.995927840009</v>
@@ -10844,13 +10844,13 @@
         <v>1752.995927840009</v>
       </c>
       <c r="Q138">
-        <v>23.9562229335429</v>
+        <v>32.56519850711402</v>
       </c>
       <c r="R138">
-        <v>23.9562229335429</v>
+        <v>32.56519850711402</v>
       </c>
       <c r="S138">
-        <v>106.0486041886265</v>
+        <v>106.5696120598403</v>
       </c>
       <c r="T138">
         <v>485.9</v>
@@ -10859,10 +10859,10 @@
         <v>1060</v>
       </c>
       <c r="V138">
-        <v>0.01366587483352632</v>
+        <v>0.01857688200521944</v>
       </c>
       <c r="W138">
-        <v>0.01366587483352632</v>
+        <v>0.01857688200521944</v>
       </c>
       <c r="X138">
         <v>2030</v>
@@ -10900,16 +10900,16 @@
         <v>92</v>
       </c>
       <c r="K139">
-        <v>98938.60040063692</v>
+        <v>98938.60040063695</v>
       </c>
       <c r="L139">
-        <v>5910.312414743242</v>
+        <v>5942.86695662938</v>
       </c>
       <c r="M139">
-        <v>5910.312414743242</v>
+        <v>5942.86695662938</v>
       </c>
       <c r="N139">
-        <v>5910.312414743242</v>
+        <v>5942.86695662938</v>
       </c>
       <c r="O139">
         <v>5516.907875722529</v>
@@ -10918,13 +10918,13 @@
         <v>5516.907875722529</v>
       </c>
       <c r="Q139">
-        <v>393.4045390207129</v>
+        <v>425.9590809068513</v>
       </c>
       <c r="R139">
-        <v>393.4045390207129</v>
+        <v>425.9590809068513</v>
       </c>
       <c r="S139">
-        <v>376.1855109277969</v>
+        <v>378.2575751628295</v>
       </c>
       <c r="T139">
         <v>91.2</v>
@@ -10933,10 +10933,10 @@
         <v>2900</v>
       </c>
       <c r="V139">
-        <v>0.07130888314302153</v>
+        <v>0.0772097505527161</v>
       </c>
       <c r="W139">
-        <v>0.07130888314302153</v>
+        <v>0.0772097505527161</v>
       </c>
       <c r="X139">
         <v>2030</v>
@@ -10977,13 +10977,13 @@
         <v>83910</v>
       </c>
       <c r="L140">
-        <v>206.3666627874487</v>
+        <v>207.498741507007</v>
       </c>
       <c r="M140">
-        <v>206.3666627874487</v>
+        <v>207.498741507007</v>
       </c>
       <c r="N140">
-        <v>206.3666627874487</v>
+        <v>207.498741507007</v>
       </c>
       <c r="O140">
         <v>207.564866114061</v>
@@ -10992,13 +10992,13 @@
         <v>207.564866114061</v>
       </c>
       <c r="Q140">
-        <v>-1.198203326612287</v>
+        <v>-0.06612460705403578</v>
       </c>
       <c r="R140">
-        <v>-1.198203326612287</v>
+        <v>-0.06612460705403578</v>
       </c>
       <c r="S140">
-        <v>21.93980218004271</v>
+        <v>22.06015874744491</v>
       </c>
       <c r="T140">
         <v>29.8</v>
@@ -11007,10 +11007,10 @@
         <v>190</v>
       </c>
       <c r="V140">
-        <v>-0.005772669281870904</v>
+        <v>-0.000318573216614121</v>
       </c>
       <c r="W140">
-        <v>-0.005772669281870904</v>
+        <v>-0.000318573216614121</v>
       </c>
       <c r="X140">
         <v>2030</v>
@@ -11048,16 +11048,16 @@
         <v>93</v>
       </c>
       <c r="K141">
-        <v>89975.2677623019</v>
+        <v>90039.78874639532</v>
       </c>
       <c r="L141">
-        <v>128.2895305917606</v>
+        <v>128.6050406823263</v>
       </c>
       <c r="M141">
-        <v>128.2895305917606</v>
+        <v>128.6050406823263</v>
       </c>
       <c r="N141">
-        <v>128.2895305917606</v>
+        <v>128.6050406823263</v>
       </c>
       <c r="O141">
         <v>126.4932043565378</v>
@@ -11066,13 +11066,13 @@
         <v>126.4932043565378</v>
       </c>
       <c r="Q141">
-        <v>1.796326235222708</v>
+        <v>2.111836325788502</v>
       </c>
       <c r="R141">
-        <v>1.796326235222708</v>
+        <v>2.111836325788502</v>
       </c>
       <c r="S141">
-        <v>9.957443140264088</v>
+        <v>9.976245220688183</v>
       </c>
       <c r="T141">
         <v>40.9</v>
@@ -11081,10 +11081,10 @@
         <v>30</v>
       </c>
       <c r="V141">
-        <v>0.01420097027631243</v>
+        <v>0.01669525518411259</v>
       </c>
       <c r="W141">
-        <v>0.01420097027631243</v>
+        <v>0.01669525518411259</v>
       </c>
       <c r="X141">
         <v>2030</v>
@@ -11122,16 +11122,16 @@
         <v>92</v>
       </c>
       <c r="K142">
-        <v>61055.77004044822</v>
+        <v>61096.29688656147</v>
       </c>
       <c r="L142">
-        <v>186.4032601901421</v>
+        <v>187.0210811148923</v>
       </c>
       <c r="M142">
-        <v>186.4032601901421</v>
+        <v>187.0210811148923</v>
       </c>
       <c r="N142">
-        <v>186.4032601901421</v>
+        <v>187.0210811148923</v>
       </c>
       <c r="O142">
         <v>179.1354550790905</v>
@@ -11140,13 +11140,13 @@
         <v>179.1354550790905</v>
       </c>
       <c r="Q142">
-        <v>7.267805111051587</v>
+        <v>7.885626035801749</v>
       </c>
       <c r="R142">
-        <v>7.267805111051587</v>
+        <v>7.885626035801749</v>
       </c>
       <c r="S142">
-        <v>14.68603819360112</v>
+        <v>14.73289945482809</v>
       </c>
       <c r="T142">
         <v>35.2</v>
@@ -11155,10 +11155,10 @@
         <v>80</v>
       </c>
       <c r="V142">
-        <v>0.0405715613798662</v>
+        <v>0.04402046502921572</v>
       </c>
       <c r="W142">
-        <v>0.0405715613798662</v>
+        <v>0.04402046502921572</v>
       </c>
       <c r="X142">
         <v>2030</v>
@@ -11199,13 +11199,13 @@
         <v>31888.09490060964</v>
       </c>
       <c r="L143">
-        <v>1738.686908893129</v>
+        <v>1748.263755568993</v>
       </c>
       <c r="M143">
-        <v>1738.686908893129</v>
+        <v>1748.263755568993</v>
       </c>
       <c r="N143">
-        <v>1738.686908893129</v>
+        <v>1748.263755568993</v>
       </c>
       <c r="O143">
         <v>1874.064125722541</v>
@@ -11214,13 +11214,13 @@
         <v>1874.064125722541</v>
       </c>
       <c r="Q143">
-        <v>-135.3772168294115</v>
+        <v>-125.8003701535483</v>
       </c>
       <c r="R143">
-        <v>-135.3772168294115</v>
+        <v>-125.8003701535483</v>
       </c>
       <c r="S143">
-        <v>375.2886217071746</v>
+        <v>377.3557457942672</v>
       </c>
       <c r="T143">
         <v>1236.2</v>
@@ -11229,10 +11229,10 @@
         <v>2090</v>
       </c>
       <c r="V143">
-        <v>-0.07223723829472332</v>
+        <v>-0.06712703606395876</v>
       </c>
       <c r="W143">
-        <v>-0.07223723829472332</v>
+        <v>-0.06712703606395876</v>
       </c>
       <c r="X143">
         <v>2030</v>
@@ -11270,16 +11270,16 @@
         <v>91</v>
       </c>
       <c r="K144">
-        <v>36133.56872341642</v>
+        <v>36134.36193967638</v>
       </c>
       <c r="L144">
-        <v>674.5885729142057</v>
+        <v>675.6714790048065</v>
       </c>
       <c r="M144">
-        <v>674.5885729142057</v>
+        <v>675.6714790048065</v>
       </c>
       <c r="N144">
-        <v>674.5885729142057</v>
+        <v>675.6714790048065</v>
       </c>
       <c r="O144">
         <v>678.1337770102322</v>
@@ -11288,13 +11288,13 @@
         <v>678.1337770102322</v>
       </c>
       <c r="Q144">
-        <v>-3.545204096026509</v>
+        <v>-2.462298005425623</v>
       </c>
       <c r="R144">
-        <v>-3.545204096026509</v>
+        <v>-2.462298005425623</v>
       </c>
       <c r="S144">
-        <v>95.13253931595113</v>
+        <v>95.28232743485827</v>
       </c>
       <c r="T144">
         <v>1212.1</v>
@@ -11303,10 +11303,10 @@
         <v>920</v>
       </c>
       <c r="V144">
-        <v>-0.005227883075897895</v>
+        <v>-0.003630991537217693</v>
       </c>
       <c r="W144">
-        <v>-0.005227883075897895</v>
+        <v>-0.003630991537217693</v>
       </c>
       <c r="X144">
         <v>2030</v>
@@ -11344,16 +11344,16 @@
         <v>91</v>
       </c>
       <c r="K145">
-        <v>41654.02816831741</v>
+        <v>41661.42474784818</v>
       </c>
       <c r="L145">
-        <v>56547.79597044526</v>
+        <v>56750.15821366566</v>
       </c>
       <c r="M145">
-        <v>56547.79597044526</v>
+        <v>56750.15821366566</v>
       </c>
       <c r="N145">
-        <v>56547.79597044526</v>
+        <v>56750.15821366566</v>
       </c>
       <c r="O145">
         <v>57659.99564606896</v>
@@ -11362,13 +11362,13 @@
         <v>57659.99564606896</v>
       </c>
       <c r="Q145">
-        <v>-1112.199675623699</v>
+        <v>-909.8374324032993</v>
       </c>
       <c r="R145">
-        <v>-1112.199675623699</v>
+        <v>-909.8374324032993</v>
       </c>
       <c r="S145">
-        <v>7500.973934076121</v>
+        <v>7528.614313881842</v>
       </c>
       <c r="T145">
         <v>3407.7</v>
@@ -11377,10 +11377,10 @@
         <v>53300</v>
       </c>
       <c r="V145">
-        <v>-0.01928893096785248</v>
+        <v>-0.01577935312357813</v>
       </c>
       <c r="W145">
-        <v>-0.01928893096785248</v>
+        <v>-0.01577935312357813</v>
       </c>
       <c r="X145">
         <v>2030</v>
@@ -11418,16 +11418,16 @@
         <v>91</v>
       </c>
       <c r="K146">
-        <v>46660.48724280273</v>
+        <v>46663.27602950118</v>
       </c>
       <c r="L146">
-        <v>21342.10748129855</v>
+        <v>21399.9978544822</v>
       </c>
       <c r="M146">
-        <v>21342.10748129855</v>
+        <v>21399.9978544822</v>
       </c>
       <c r="N146">
-        <v>21342.10748129855</v>
+        <v>21399.9978544822</v>
       </c>
       <c r="O146">
         <v>22612.12127609656</v>
@@ -11436,13 +11436,13 @@
         <v>22612.12127609656</v>
       </c>
       <c r="Q146">
-        <v>-1270.013794798018</v>
+        <v>-1212.123421614364</v>
       </c>
       <c r="R146">
-        <v>-1270.013794798018</v>
+        <v>-1212.123421614364</v>
       </c>
       <c r="S146">
-        <v>2242.058415654637</v>
+        <v>2247.861695754209</v>
       </c>
       <c r="T146">
         <v>4295.5</v>
@@ -11451,10 +11451,10 @@
         <v>22660</v>
       </c>
       <c r="V146">
-        <v>-0.05616517704336563</v>
+        <v>-0.05360502921482684</v>
       </c>
       <c r="W146">
-        <v>-0.05616517704336563</v>
+        <v>-0.05360502921482684</v>
       </c>
       <c r="X146">
         <v>2030</v>
@@ -11492,16 +11492,16 @@
         <v>91</v>
       </c>
       <c r="K147">
-        <v>59424.2704731406</v>
+        <v>59424.31552181094</v>
       </c>
       <c r="L147">
-        <v>643.3946927081064</v>
+        <v>646.9304343007432</v>
       </c>
       <c r="M147">
-        <v>643.3946927081064</v>
+        <v>646.9304343007432</v>
       </c>
       <c r="N147">
-        <v>643.3946927081064</v>
+        <v>646.9304343007432</v>
       </c>
       <c r="O147">
         <v>659.08843047457</v>
@@ -11510,13 +11510,13 @@
         <v>659.08843047457</v>
       </c>
       <c r="Q147">
-        <v>-15.69373776646364</v>
+        <v>-12.15799617382686</v>
       </c>
       <c r="R147">
-        <v>-15.69373776646364</v>
+        <v>-12.15799617382686</v>
       </c>
       <c r="S147">
-        <v>55.0495990958137</v>
+        <v>55.35212557936029</v>
       </c>
       <c r="T147">
         <v>619.5000000000001</v>
@@ -11525,10 +11525,10 @@
         <v>100</v>
       </c>
       <c r="V147">
-        <v>-0.02381127788142711</v>
+        <v>-0.01844668425612116</v>
       </c>
       <c r="W147">
-        <v>-0.02381127788142711</v>
+        <v>-0.01844668425612116</v>
       </c>
       <c r="X147">
         <v>2030</v>
@@ -11566,16 +11566,16 @@
         <v>91</v>
       </c>
       <c r="K148">
-        <v>53677.24649322512</v>
+        <v>53682.07452854787</v>
       </c>
       <c r="L148">
-        <v>43039.58102091397</v>
+        <v>43071.62507337928</v>
       </c>
       <c r="M148">
-        <v>43039.58102091397</v>
+        <v>43071.62507337928</v>
       </c>
       <c r="N148">
-        <v>43039.58102091397</v>
+        <v>43071.62507337928</v>
       </c>
       <c r="O148">
         <v>41935.23650636454</v>
@@ -11584,13 +11584,13 @@
         <v>41935.23650636454</v>
       </c>
       <c r="Q148">
-        <v>1104.344514549433</v>
+        <v>1136.388567014743</v>
       </c>
       <c r="R148">
-        <v>1104.344514549433</v>
+        <v>1136.388567014743</v>
       </c>
       <c r="S148">
-        <v>3873.587434784652</v>
+        <v>3877.312540408357</v>
       </c>
       <c r="T148">
         <v>1057.8</v>
@@ -11599,10 +11599,10 @@
         <v>36080</v>
       </c>
       <c r="V148">
-        <v>0.02633452453241384</v>
+        <v>0.02709865644473645</v>
       </c>
       <c r="W148">
-        <v>0.02633452453241384</v>
+        <v>0.02709865644473645</v>
       </c>
       <c r="X148">
         <v>2030</v>
@@ -11640,16 +11640,16 @@
         <v>91</v>
       </c>
       <c r="K149">
-        <v>48370.45278678316</v>
+        <v>48369.99285668202</v>
       </c>
       <c r="L149">
-        <v>8871.610363768536</v>
+        <v>8912.45488216241</v>
       </c>
       <c r="M149">
-        <v>8871.610363768536</v>
+        <v>8912.45488216241</v>
       </c>
       <c r="N149">
-        <v>8871.610363768536</v>
+        <v>8912.45488216241</v>
       </c>
       <c r="O149">
         <v>8699.566232337553</v>
@@ -11658,13 +11658,13 @@
         <v>8699.566232337553</v>
       </c>
       <c r="Q149">
-        <v>172.0441314309828</v>
+        <v>212.8886498248576</v>
       </c>
       <c r="R149">
-        <v>172.0441314309828</v>
+        <v>212.8886498248576</v>
       </c>
       <c r="S149">
-        <v>893.3778373688855</v>
+        <v>897.5272553009216</v>
       </c>
       <c r="T149">
         <v>922.0000000000001</v>
@@ -11673,10 +11673,10 @@
         <v>8040</v>
       </c>
       <c r="V149">
-        <v>0.01977617352822371</v>
+        <v>0.02447117984268221</v>
       </c>
       <c r="W149">
-        <v>0.01977617352822371</v>
+        <v>0.02447117984268221</v>
       </c>
       <c r="X149">
         <v>2030</v>
@@ -11714,16 +11714,16 @@
         <v>91</v>
       </c>
       <c r="K150">
-        <v>47448.2059112256</v>
+        <v>47464.219197206</v>
       </c>
       <c r="L150">
-        <v>65035.59531123676</v>
+        <v>65280.59846683565</v>
       </c>
       <c r="M150">
-        <v>65035.59531123676</v>
+        <v>65280.59846683565</v>
       </c>
       <c r="N150">
-        <v>65035.59531123676</v>
+        <v>65280.59846683565</v>
       </c>
       <c r="O150">
         <v>67687.09926290459</v>
@@ -11732,13 +11732,13 @@
         <v>67687.09926290459</v>
       </c>
       <c r="Q150">
-        <v>-2651.503951667837</v>
+        <v>-2406.500796068947</v>
       </c>
       <c r="R150">
-        <v>-2651.503951667837</v>
+        <v>-2406.500796068947</v>
       </c>
       <c r="S150">
-        <v>7609.424771767754</v>
+        <v>7636.380542133733</v>
       </c>
       <c r="T150">
         <v>4474.700000000001</v>
@@ -11747,10 +11747,10 @@
         <v>64930</v>
       </c>
       <c r="V150">
-        <v>-0.03917295881404352</v>
+        <v>-0.03555331551026906</v>
       </c>
       <c r="W150">
-        <v>-0.03917295881404352</v>
+        <v>-0.03555331551026906</v>
       </c>
       <c r="X150">
         <v>2030</v>
@@ -16302,16 +16302,16 @@
         <v>91</v>
       </c>
       <c r="K212">
-        <v>61934.36995476879</v>
+        <v>61920.10262590968</v>
       </c>
       <c r="L212">
-        <v>53584.70486200643</v>
+        <v>53939.13625448258</v>
       </c>
       <c r="M212">
-        <v>53584.70486200643</v>
+        <v>53939.13625448258</v>
       </c>
       <c r="N212">
-        <v>192245.5413598886</v>
+        <v>193390.1309088592</v>
       </c>
       <c r="O212">
         <v>56442.17259301741</v>
@@ -16320,13 +16320,13 @@
         <v>199629</v>
       </c>
       <c r="Q212">
-        <v>-2857.467731010984</v>
+        <v>-2503.036338534839</v>
       </c>
       <c r="R212">
-        <v>-7383.458640111465</v>
+        <v>-6238.869091140834</v>
       </c>
       <c r="S212">
-        <v>5090.010723792841</v>
+        <v>5124.054316586005</v>
       </c>
       <c r="T212">
         <v>29773.4</v>
@@ -16335,10 +16335,10 @@
         <v>190620</v>
       </c>
       <c r="V212">
-        <v>-0.05062646598696818</v>
+        <v>-0.04434691691588951</v>
       </c>
       <c r="W212">
-        <v>-0.03698590204885795</v>
+        <v>-0.03125231850653379</v>
       </c>
       <c r="X212">
         <v>2030</v>
@@ -16376,16 +16376,16 @@
         <v>92</v>
       </c>
       <c r="K213">
-        <v>129986.9779087832</v>
+        <v>129985.6367072114</v>
       </c>
       <c r="L213">
-        <v>3870.026440472842</v>
+        <v>3893.626612243138</v>
       </c>
       <c r="M213">
-        <v>3870.026440472842</v>
+        <v>3893.626612243138</v>
       </c>
       <c r="N213">
-        <v>14153.39119607458</v>
+        <v>14230.79928944954</v>
       </c>
       <c r="O213">
         <v>3989.912572624614</v>
@@ -16394,13 +16394,13 @@
         <v>14428.19434145158</v>
       </c>
       <c r="Q213">
-        <v>-119.8861321517716</v>
+        <v>-96.28596038147589</v>
       </c>
       <c r="R213">
-        <v>-274.803145377</v>
+        <v>-197.3950520020408</v>
       </c>
       <c r="S213">
-        <v>291.5742179430147</v>
+        <v>293.3529260155012</v>
       </c>
       <c r="T213">
         <v>3480</v>
@@ -16409,10 +16409,10 @@
         <v>13740</v>
       </c>
       <c r="V213">
-        <v>-0.03004730804738134</v>
+        <v>-0.02413234842339861</v>
       </c>
       <c r="W213">
-        <v>-0.01904626032014986</v>
+        <v>-0.01368120274308569</v>
       </c>
       <c r="X213">
         <v>2030</v>
@@ -16450,16 +16450,16 @@
         <v>92</v>
       </c>
       <c r="K214">
-        <v>80984.96853148688</v>
+        <v>80982.06003932894</v>
       </c>
       <c r="L214">
-        <v>2681.565933109704</v>
+        <v>2697.099473049806</v>
       </c>
       <c r="M214">
-        <v>2681.565933109704</v>
+        <v>2697.099473049806</v>
       </c>
       <c r="N214">
-        <v>10137.63488513185</v>
+        <v>10190.4293677819</v>
       </c>
       <c r="O214">
         <v>2721.409348739371</v>
@@ -16468,13 +16468,13 @@
         <v>10200.96227902136</v>
       </c>
       <c r="Q214">
-        <v>-39.84341562966665</v>
+        <v>-24.30987568956516</v>
       </c>
       <c r="R214">
-        <v>-63.32739388951268</v>
+        <v>-10.53291123945928</v>
       </c>
       <c r="S214">
-        <v>230.5230116284792</v>
+        <v>231.856231106926</v>
       </c>
       <c r="T214">
         <v>3317.5</v>
@@ -16483,10 +16483,10 @@
         <v>8860</v>
       </c>
       <c r="V214">
-        <v>-0.01464072857988938</v>
+        <v>-0.008932825817191426</v>
       </c>
       <c r="W214">
-        <v>-0.006207982360619811</v>
+        <v>-0.001032540945781222</v>
       </c>
       <c r="X214">
         <v>2030</v>
@@ -16524,16 +16524,16 @@
         <v>92</v>
       </c>
       <c r="K215">
-        <v>105147.08426074</v>
+        <v>105117.6964689608</v>
       </c>
       <c r="L215">
-        <v>674.8743097914603</v>
+        <v>678.0073962351355</v>
       </c>
       <c r="M215">
-        <v>674.8743097914603</v>
+        <v>678.0073962351355</v>
       </c>
       <c r="N215">
-        <v>2431.627659347741</v>
+        <v>2442.204251031421</v>
       </c>
       <c r="O215">
         <v>699.6641706740414</v>
@@ -16542,13 +16542,13 @@
         <v>2504.362581707458</v>
       </c>
       <c r="Q215">
-        <v>-24.78986088258114</v>
+        <v>-21.65677443890593</v>
       </c>
       <c r="R215">
-        <v>-72.73492235971617</v>
+        <v>-62.15833067603671</v>
       </c>
       <c r="S215">
-        <v>40.30150760354638</v>
+        <v>40.48613961341635</v>
       </c>
       <c r="T215">
         <v>922.5</v>
@@ -16557,10 +16557,10 @@
         <v>2160</v>
       </c>
       <c r="V215">
-        <v>-0.03543108525723008</v>
+        <v>-0.03095309913903731</v>
       </c>
       <c r="W215">
-        <v>-0.0290432874580509</v>
+        <v>-0.02482002052340903</v>
       </c>
       <c r="X215">
         <v>2030</v>
@@ -16598,16 +16598,16 @@
         <v>92</v>
       </c>
       <c r="K216">
-        <v>96853.91631322399</v>
+        <v>96847.94903397649</v>
       </c>
       <c r="L216">
-        <v>4202.834962863623</v>
+        <v>4225.287448011863</v>
       </c>
       <c r="M216">
-        <v>4202.834962863623</v>
+        <v>4225.287448011863</v>
       </c>
       <c r="N216">
-        <v>16430.3306199143</v>
+        <v>16508.39282013427</v>
       </c>
       <c r="O216">
         <v>4182.664525935822</v>
@@ -16616,13 +16616,13 @@
         <v>16231.25645227748</v>
       </c>
       <c r="Q216">
-        <v>20.17043692780135</v>
+        <v>42.6229220760415</v>
       </c>
       <c r="R216">
-        <v>199.0741676368161</v>
+        <v>277.1363678567905</v>
       </c>
       <c r="S216">
-        <v>284.6003380915761</v>
+        <v>286.1398393573929</v>
       </c>
       <c r="T216">
         <v>438.9</v>
@@ -16631,10 +16631,10 @@
         <v>13950</v>
       </c>
       <c r="V216">
-        <v>0.004822389365135242</v>
+        <v>0.01019037549192524</v>
       </c>
       <c r="W216">
-        <v>0.01226486490569146</v>
+        <v>0.0170742399808429</v>
       </c>
       <c r="X216">
         <v>2030</v>
@@ -16672,16 +16672,16 @@
         <v>92</v>
       </c>
       <c r="K217">
-        <v>76427.43827412845</v>
+        <v>76423.53581209209</v>
       </c>
       <c r="L217">
-        <v>379.9633763034433</v>
+        <v>383.3326035477158</v>
       </c>
       <c r="M217">
-        <v>379.9633763034433</v>
+        <v>383.3326035477158</v>
       </c>
       <c r="N217">
-        <v>1259.291455025361</v>
+        <v>1270.401438297547</v>
       </c>
       <c r="O217">
         <v>391.8535237411929</v>
@@ -16690,13 +16690,13 @@
         <v>1284.525272586331</v>
       </c>
       <c r="Q217">
-        <v>-11.89014743774953</v>
+        <v>-8.520920193477082</v>
       </c>
       <c r="R217">
-        <v>-25.23381756096978</v>
+        <v>-14.12383428878388</v>
       </c>
       <c r="S217">
-        <v>35.38934356565523</v>
+        <v>35.70190897951672</v>
       </c>
       <c r="T217">
         <v>103.5</v>
@@ -16705,10 +16705,10 @@
         <v>1020</v>
       </c>
       <c r="V217">
-        <v>-0.0303433469839169</v>
+        <v>-0.02174516669423875</v>
       </c>
       <c r="W217">
-        <v>-0.01964446951686882</v>
+        <v>-0.01099537283555832</v>
       </c>
       <c r="X217">
         <v>2030</v>
@@ -16746,16 +16746,16 @@
         <v>92</v>
       </c>
       <c r="K218">
-        <v>80126.06344300175</v>
+        <v>80098.97296433384</v>
       </c>
       <c r="L218">
-        <v>66.71736564702717</v>
+        <v>67.11585701434404</v>
       </c>
       <c r="M218">
-        <v>66.71736564702717</v>
+        <v>67.11585701434404</v>
       </c>
       <c r="N218">
-        <v>309.9217129698541</v>
+        <v>311.4906399280085</v>
       </c>
       <c r="O218">
         <v>68.83077471292034</v>
@@ -16764,13 +16764,13 @@
         <v>318.263316043786</v>
       </c>
       <c r="Q218">
-        <v>-2.11340906589318</v>
+        <v>-1.714917698576301</v>
       </c>
       <c r="R218">
-        <v>-8.341603073931878</v>
+        <v>-6.772676115777472</v>
       </c>
       <c r="S218">
-        <v>5.276417452312211</v>
+        <v>5.30772069274869</v>
       </c>
       <c r="T218">
         <v>34</v>
@@ -16779,10 +16779,10 @@
         <v>390</v>
       </c>
       <c r="V218">
-        <v>-0.03070442072906769</v>
+        <v>-0.02491498469585568</v>
       </c>
       <c r="W218">
-        <v>-0.0262097535387467</v>
+        <v>-0.02128010290336352</v>
       </c>
       <c r="X218">
         <v>2030</v>
@@ -16823,13 +16823,13 @@
         <v>38370</v>
       </c>
       <c r="L219">
-        <v>21.98921302961482</v>
+        <v>22.2139331449696</v>
       </c>
       <c r="M219">
-        <v>21.98921302961482</v>
+        <v>22.2139331449696</v>
       </c>
       <c r="N219">
-        <v>74.79988980227152</v>
+        <v>75.5659344358092</v>
       </c>
       <c r="O219">
         <v>23.32788826273601</v>
@@ -16838,13 +16838,13 @@
         <v>78.70029260136461</v>
       </c>
       <c r="Q219">
-        <v>-1.33867523312119</v>
+        <v>-1.113955117766409</v>
       </c>
       <c r="R219">
-        <v>-3.900402799093087</v>
+        <v>-3.134358165555412</v>
       </c>
       <c r="S219">
-        <v>2.799512334151499</v>
+        <v>2.828122122679191</v>
       </c>
       <c r="T219">
         <v>161</v>
@@ -16853,10 +16853,10 @@
         <v>30</v>
       </c>
       <c r="V219">
-        <v>-0.05738518712212761</v>
+        <v>-0.04775207705130523</v>
       </c>
       <c r="W219">
-        <v>-0.04956020708651668</v>
+        <v>-0.03982651222698331</v>
       </c>
       <c r="X219">
         <v>2030</v>
@@ -16897,13 +16897,13 @@
         <v>35930</v>
       </c>
       <c r="L220">
-        <v>261.9518133944877</v>
+        <v>263.8339130771171</v>
       </c>
       <c r="M220">
-        <v>261.9518133944877</v>
+        <v>263.8339130771171</v>
       </c>
       <c r="N220">
-        <v>985.5884110092603</v>
+        <v>991.7979586493966</v>
       </c>
       <c r="O220">
         <v>272.807444874833</v>
@@ -16912,13 +16912,13 @@
         <v>1011.632816072309</v>
       </c>
       <c r="Q220">
-        <v>-10.85563148034538</v>
+        <v>-8.973531797715907</v>
       </c>
       <c r="R220">
-        <v>-26.0444050630482</v>
+        <v>-19.83485742291191</v>
       </c>
       <c r="S220">
-        <v>37.23242921406518</v>
+        <v>37.49994079300504</v>
       </c>
       <c r="T220">
         <v>1756.5</v>
@@ -16927,10 +16927,10 @@
         <v>1060</v>
       </c>
       <c r="V220">
-        <v>-0.03979228457392744</v>
+        <v>-0.03289328046686211</v>
       </c>
       <c r="W220">
-        <v>-0.02574491915373633</v>
+        <v>-0.01960677541078716</v>
       </c>
       <c r="X220">
         <v>2030</v>
@@ -16968,16 +16968,16 @@
         <v>91</v>
       </c>
       <c r="K221">
-        <v>75188.3128366694</v>
+        <v>75173.100647443</v>
       </c>
       <c r="L221">
-        <v>1328.711364325296</v>
+        <v>1336.039090945878</v>
       </c>
       <c r="M221">
-        <v>1328.711364325296</v>
+        <v>1336.039090945878</v>
       </c>
       <c r="N221">
-        <v>5215.801675911508</v>
+        <v>5241.427404461399</v>
       </c>
       <c r="O221">
         <v>1393.197131603846</v>
@@ -16986,13 +16986,13 @@
         <v>5427.43390674915</v>
       </c>
       <c r="Q221">
-        <v>-64.48576727854925</v>
+        <v>-57.15804065796738</v>
       </c>
       <c r="R221">
-        <v>-211.6322308376421</v>
+        <v>-186.0065022877516</v>
       </c>
       <c r="S221">
-        <v>117.2217209344061</v>
+        <v>117.8707145462447</v>
       </c>
       <c r="T221">
         <v>1534.8</v>
@@ -17001,10 +17001,10 @@
         <v>4940</v>
       </c>
       <c r="V221">
-        <v>-0.04628617574335181</v>
+        <v>-0.04102652766171515</v>
       </c>
       <c r="W221">
-        <v>-0.03899305536903399</v>
+        <v>-0.0342715370621921</v>
       </c>
       <c r="X221">
         <v>2030</v>
@@ -17042,16 +17042,16 @@
         <v>91</v>
       </c>
       <c r="K222">
-        <v>47146.01082780237</v>
+        <v>47145.51399921258</v>
       </c>
       <c r="L222">
-        <v>3930.253795278042</v>
+        <v>3955.838696567285</v>
       </c>
       <c r="M222">
-        <v>3930.253795278042</v>
+        <v>3955.838696567285</v>
       </c>
       <c r="N222">
-        <v>14484.60056290628</v>
+        <v>14569.27814273722</v>
       </c>
       <c r="O222">
         <v>4304.507929494404</v>
@@ -17060,13 +17060,13 @@
         <v>15675.88588594714</v>
       </c>
       <c r="Q222">
-        <v>-374.2541342163627</v>
+        <v>-348.6692329271191</v>
       </c>
       <c r="R222">
-        <v>-1191.285323040858</v>
+        <v>-1106.607743209917</v>
       </c>
       <c r="S222">
-        <v>388.3815689371806</v>
+        <v>390.8850191541526</v>
       </c>
       <c r="T222">
         <v>6865</v>
@@ -17075,10 +17075,10 @@
         <v>16770</v>
       </c>
       <c r="V222">
-        <v>-0.08694469619906625</v>
+        <v>-0.08100095031491156</v>
       </c>
       <c r="W222">
-        <v>-0.07599476876192382</v>
+        <v>-0.07059299558961135</v>
       </c>
       <c r="X222">
         <v>2030</v>
@@ -17119,13 +17119,13 @@
         <v>62350</v>
       </c>
       <c r="L223">
-        <v>263.8872409322486</v>
+        <v>265.4682008335099</v>
       </c>
       <c r="M223">
-        <v>263.8872409322486</v>
+        <v>265.4682008335099</v>
       </c>
       <c r="N223">
-        <v>1027.612031526638</v>
+        <v>1032.892308980246</v>
       </c>
       <c r="O223">
         <v>274.4721059587123</v>
@@ -17134,13 +17134,13 @@
         <v>1055.808256502304</v>
       </c>
       <c r="Q223">
-        <v>-10.58486502646366</v>
+        <v>-9.00390512520238</v>
       </c>
       <c r="R223">
-        <v>-28.19622497566593</v>
+        <v>-22.9159475220581</v>
       </c>
       <c r="S223">
-        <v>24.92986530850494</v>
+        <v>25.07922121240296</v>
       </c>
       <c r="T223">
         <v>405</v>
@@ -17149,10 +17149,10 @@
         <v>640</v>
       </c>
       <c r="V223">
-        <v>-0.03856444715754066</v>
+        <v>-0.03280444507740542</v>
       </c>
       <c r="W223">
-        <v>-0.02670581973764324</v>
+        <v>-0.02170464890848114</v>
       </c>
       <c r="X223">
         <v>2030</v>
@@ -17190,16 +17190,16 @@
         <v>91</v>
       </c>
       <c r="K224">
-        <v>61021.57687621623</v>
+        <v>61020.8147543179</v>
       </c>
       <c r="L224">
-        <v>2559.048329935626</v>
+        <v>2577.937371786481</v>
       </c>
       <c r="M224">
-        <v>2559.048329935626</v>
+        <v>2577.937371786481</v>
       </c>
       <c r="N224">
-        <v>8743.261727909427</v>
+        <v>8801.928150771066</v>
       </c>
       <c r="O224">
         <v>2557.21991147307</v>
@@ -17208,13 +17208,13 @@
         <v>8582.90129276398</v>
       </c>
       <c r="Q224">
-        <v>1.828418462555874</v>
+        <v>20.71746031341036</v>
       </c>
       <c r="R224">
-        <v>160.3604351454469</v>
+        <v>219.026858007086</v>
       </c>
       <c r="S224">
-        <v>242.3056845985553</v>
+        <v>244.095371083281</v>
       </c>
       <c r="T224">
         <v>1352.6</v>
@@ -17223,10 +17223,10 @@
         <v>8320</v>
       </c>
       <c r="V224">
-        <v>0.0007150024346176098</v>
+        <v>0.008101555998551644</v>
       </c>
       <c r="W224">
-        <v>0.01868370958438525</v>
+        <v>0.02551897668819073</v>
       </c>
       <c r="X224">
         <v>2030</v>
@@ -17264,16 +17264,16 @@
         <v>91</v>
       </c>
       <c r="K225">
-        <v>49104.6751600152</v>
+        <v>49100.96160363618</v>
       </c>
       <c r="L225">
-        <v>30159.18754487261</v>
+        <v>30364.75827151085</v>
       </c>
       <c r="M225">
-        <v>30159.18754487261</v>
+        <v>30364.75827151085</v>
       </c>
       <c r="N225">
-        <v>106342.3979006518</v>
+        <v>106995.4957729267</v>
       </c>
       <c r="O225">
         <v>32213.37987692794</v>
@@ -17282,13 +17282,13 @@
         <v>111792.2099327841</v>
       </c>
       <c r="Q225">
-        <v>-2054.192332055329</v>
+        <v>-1848.621605417087</v>
       </c>
       <c r="R225">
-        <v>-5449.812032132264</v>
+        <v>-4796.71415985738</v>
       </c>
       <c r="S225">
-        <v>3007.347968650809</v>
+        <v>3027.875759039654</v>
       </c>
       <c r="T225">
         <v>2950.1</v>
@@ -17297,10 +17297,10 @@
         <v>108350</v>
       </c>
       <c r="V225">
-        <v>-0.06376829565551408</v>
+        <v>-0.0573867632791031</v>
       </c>
       <c r="W225">
-        <v>-0.04874947937256992</v>
+        <v>-0.04290740976264303</v>
       </c>
       <c r="X225">
         <v>2030</v>
@@ -17338,16 +17338,16 @@
         <v>91</v>
       </c>
       <c r="K226">
-        <v>43058.54378048273</v>
+        <v>43061.86973994111</v>
       </c>
       <c r="L226">
-        <v>3183.693172050409</v>
+        <v>3208.57738651448</v>
       </c>
       <c r="M226">
-        <v>3183.693172050409</v>
+        <v>3208.57738651448</v>
       </c>
       <c r="N226">
-        <v>10649.2816317077</v>
+        <v>10728.02742927463</v>
       </c>
       <c r="O226">
         <v>3348.925387993901</v>
@@ -17356,13 +17356,13 @@
         <v>11036.86337349168</v>
       </c>
       <c r="Q226">
-        <v>-165.2322159434912</v>
+        <v>-140.3480014794204</v>
       </c>
       <c r="R226">
-        <v>-387.5817417839826</v>
+        <v>-308.8359442170531</v>
       </c>
       <c r="S226">
-        <v>382.1271375305843</v>
+        <v>385.0754028690835</v>
       </c>
       <c r="T226">
         <v>6452</v>
@@ -17371,10 +17371,10 @@
         <v>10390</v>
       </c>
       <c r="V226">
-        <v>-0.04933887644551849</v>
+        <v>-0.04190836916898073</v>
       </c>
       <c r="W226">
-        <v>-0.03511701909030384</v>
+        <v>-0.02798222047024835</v>
       </c>
       <c r="X226">
         <v>2030</v>
@@ -22296,16 +22296,16 @@
         <v>91</v>
       </c>
       <c r="K293">
-        <v>59283.76179622777</v>
+        <v>59281.24248526189</v>
       </c>
       <c r="L293">
-        <v>227787.2466521752</v>
+        <v>228456.4599002268</v>
       </c>
       <c r="M293">
-        <v>227787.2466521752</v>
+        <v>228456.4599002268</v>
       </c>
       <c r="N293">
-        <v>488052.933079506</v>
+        <v>488166.0318784869</v>
       </c>
       <c r="O293">
         <v>223902.0572615974</v>
@@ -22314,13 +22314,13 @@
         <v>482939.9999999999</v>
       </c>
       <c r="Q293">
-        <v>3885.189390577871</v>
+        <v>4554.402638629457</v>
       </c>
       <c r="R293">
-        <v>5112.933079506096</v>
+        <v>5226.031878486916</v>
       </c>
       <c r="S293">
-        <v>21924.93070931515</v>
+        <v>21989.65439439634</v>
       </c>
       <c r="T293">
         <v>45284.6</v>
@@ -22329,10 +22329,10 @@
         <v>474500</v>
       </c>
       <c r="V293">
-        <v>0.01735218263777981</v>
+        <v>0.02034104864569553</v>
       </c>
       <c r="W293">
-        <v>0.0105870979407506</v>
+        <v>0.0108212860365406</v>
       </c>
       <c r="X293">
         <v>2030</v>
@@ -22370,16 +22370,16 @@
         <v>92</v>
       </c>
       <c r="K294">
-        <v>132552.2115382741</v>
+        <v>132547.0127918345</v>
       </c>
       <c r="L294">
-        <v>12958.81390081448</v>
+        <v>12997.91723610492</v>
       </c>
       <c r="M294">
-        <v>12958.81390081448</v>
+        <v>12997.91723610492</v>
       </c>
       <c r="N294">
-        <v>37848.68370247383</v>
+        <v>37779.88810624615</v>
       </c>
       <c r="O294">
         <v>12700.55302866645</v>
@@ -22388,13 +22388,13 @@
         <v>37020.26413249301</v>
       </c>
       <c r="Q294">
-        <v>258.2608721480265</v>
+        <v>297.3642074384643</v>
       </c>
       <c r="R294">
-        <v>828.4195699808261</v>
+        <v>759.6239737531432</v>
       </c>
       <c r="S294">
-        <v>964.0245604729455</v>
+        <v>966.9493657441283</v>
       </c>
       <c r="T294">
         <v>5121.200000000001</v>
@@ -22403,10 +22403,10 @@
         <v>35740</v>
       </c>
       <c r="V294">
-        <v>0.02033461626159941</v>
+        <v>0.02341348496929879</v>
       </c>
       <c r="W294">
-        <v>0.02237746243559929</v>
+        <v>0.02051913976179372</v>
       </c>
       <c r="X294">
         <v>2030</v>
@@ -22444,16 +22444,16 @@
         <v>92</v>
       </c>
       <c r="K295">
-        <v>82230.1945022748</v>
+        <v>82227.15174492514</v>
       </c>
       <c r="L295">
-        <v>8908.128272691813</v>
+        <v>8934.056888690948</v>
       </c>
       <c r="M295">
-        <v>8908.128272691813</v>
+        <v>8934.056888690948</v>
       </c>
       <c r="N295">
-        <v>28398.77416358429</v>
+        <v>28328.73037459573</v>
       </c>
       <c r="O295">
         <v>8560.357866447192</v>
@@ -22462,13 +22462,13 @@
         <v>27483.85525188817</v>
       </c>
       <c r="Q295">
-        <v>347.770406244621</v>
+        <v>373.6990222437562</v>
       </c>
       <c r="R295">
-        <v>914.9189116961243</v>
+        <v>844.8751227075627</v>
       </c>
       <c r="S295">
-        <v>765.7141279346894</v>
+        <v>767.9467199610327</v>
       </c>
       <c r="T295">
         <v>4888.6</v>
@@ -22477,10 +22477,10 @@
         <v>26150</v>
       </c>
       <c r="V295">
-        <v>0.04062568547603913</v>
+        <v>0.04365460277174751</v>
       </c>
       <c r="W295">
-        <v>0.03328932216062623</v>
+        <v>0.03074077908518744</v>
       </c>
       <c r="X295">
         <v>2030</v>
@@ -22518,16 +22518,16 @@
         <v>92</v>
       </c>
       <c r="K296">
-        <v>115437.0745639017</v>
+        <v>115423.2020807891</v>
       </c>
       <c r="L296">
-        <v>3304.434987384325</v>
+        <v>3311.189177744137</v>
       </c>
       <c r="M296">
-        <v>3304.434987384325</v>
+        <v>3311.189177744137</v>
       </c>
       <c r="N296">
-        <v>17047.10543658827</v>
+        <v>16928.60849169311</v>
       </c>
       <c r="O296">
         <v>3140.240207736526</v>
@@ -22536,13 +22536,13 @@
         <v>15861.85931612553</v>
       </c>
       <c r="Q296">
-        <v>164.1947796477989</v>
+        <v>170.948970007611</v>
       </c>
       <c r="R296">
-        <v>1185.246120462734</v>
+        <v>1066.749175567582</v>
       </c>
       <c r="S296">
-        <v>203.7561248172045</v>
+        <v>204.1638720146704</v>
       </c>
       <c r="T296">
         <v>1564.1</v>
@@ -22551,10 +22551,10 @@
         <v>11450</v>
       </c>
       <c r="V296">
-        <v>0.05228733115488318</v>
+        <v>0.05443818265445063</v>
       </c>
       <c r="W296">
-        <v>0.07472302564541004</v>
+        <v>0.06725246733736316</v>
       </c>
       <c r="X296">
         <v>2030</v>
@@ -22592,16 +22592,16 @@
         <v>92</v>
       </c>
       <c r="K297">
-        <v>96439.48107244277</v>
+        <v>96437.97196018857</v>
       </c>
       <c r="L297">
-        <v>18304.1076679145</v>
+        <v>18347.7141461441</v>
       </c>
       <c r="M297">
-        <v>18304.1076679145</v>
+        <v>18347.7141461441</v>
       </c>
       <c r="N297">
-        <v>79224.83032220884</v>
+        <v>78784.96968081981</v>
       </c>
       <c r="O297">
         <v>17428.99721743924</v>
@@ -22610,13 +22610,13 @@
         <v>75836.85755341357</v>
       </c>
       <c r="Q297">
-        <v>875.1104504752657</v>
+        <v>918.7169287048637</v>
       </c>
       <c r="R297">
-        <v>3387.972768795269</v>
+        <v>2948.112127406232</v>
       </c>
       <c r="S297">
-        <v>1240.615926723505</v>
+        <v>1243.596043788462</v>
       </c>
       <c r="T297">
         <v>714.5000000000001</v>
@@ -22625,10 +22625,10 @@
         <v>77330</v>
       </c>
       <c r="V297">
-        <v>0.05021002869858979</v>
+        <v>0.05271197862064073</v>
       </c>
       <c r="W297">
-        <v>0.04467448781628439</v>
+        <v>0.0388743972590084</v>
       </c>
       <c r="X297">
         <v>2030</v>
@@ -22666,16 +22666,16 @@
         <v>92</v>
       </c>
       <c r="K298">
-        <v>78659.94212283446</v>
+        <v>78643.12035573325</v>
       </c>
       <c r="L298">
-        <v>742.6397886930149</v>
+        <v>746.0624906191823</v>
       </c>
       <c r="M298">
-        <v>742.6397886930149</v>
+        <v>746.0624906191823</v>
       </c>
       <c r="N298">
-        <v>7279.251525093083</v>
+        <v>7227.783878986235</v>
       </c>
       <c r="O298">
         <v>743.5646096336915</v>
@@ -22684,13 +22684,13 @@
         <v>6972.351906237904</v>
       </c>
       <c r="Q298">
-        <v>-0.9248209406765682</v>
+        <v>2.497880985490838</v>
       </c>
       <c r="R298">
-        <v>306.8996188551791</v>
+        <v>255.4319727483316</v>
       </c>
       <c r="S298">
-        <v>73.63148202965571</v>
+        <v>73.96557213846162</v>
       </c>
       <c r="T298">
         <v>224.3</v>
@@ -22699,10 +22699,10 @@
         <v>6470</v>
       </c>
       <c r="V298">
-        <v>-0.001243766753681527</v>
+        <v>0.003359332804611814</v>
       </c>
       <c r="W298">
-        <v>0.04401665650016998</v>
+        <v>0.03663498001582596</v>
       </c>
       <c r="X298">
         <v>2030</v>
@@ -22740,16 +22740,16 @@
         <v>92</v>
       </c>
       <c r="K299">
-        <v>150162.5117650926</v>
+        <v>150174.8380548663</v>
       </c>
       <c r="L299">
-        <v>44.42671534225047</v>
+        <v>44.48193364951828</v>
       </c>
       <c r="M299">
-        <v>44.42671534225047</v>
+        <v>44.48193364951828</v>
       </c>
       <c r="N299">
-        <v>300.4492600726056</v>
+        <v>297.6700837107662</v>
       </c>
       <c r="O299">
         <v>40.27150559824349</v>
@@ -22758,13 +22758,13 @@
         <v>284.9611074355079</v>
       </c>
       <c r="Q299">
-        <v>4.155209744006989</v>
+        <v>4.210428051274789</v>
       </c>
       <c r="R299">
-        <v>15.4881526370977</v>
+        <v>12.70897627525829</v>
       </c>
       <c r="S299">
-        <v>1.619090547786136</v>
+        <v>1.620685099736256</v>
       </c>
       <c r="T299">
         <v>102.3</v>
@@ -22773,10 +22773,10 @@
         <v>240</v>
       </c>
       <c r="V299">
-        <v>0.103179895618013</v>
+        <v>0.1045510464217269</v>
       </c>
       <c r="W299">
-        <v>0.05435181234548984</v>
+        <v>0.04459898541815772</v>
       </c>
       <c r="X299">
         <v>2030</v>
@@ -22814,16 +22814,16 @@
         <v>92</v>
       </c>
       <c r="K300">
-        <v>77592.95720661865</v>
+        <v>77594.18872371687</v>
       </c>
       <c r="L300">
-        <v>283.976682647955</v>
+        <v>284.4306760560283</v>
       </c>
       <c r="M300">
-        <v>283.976682647955</v>
+        <v>284.4306760560283</v>
       </c>
       <c r="N300">
-        <v>3705.429287097429</v>
+        <v>3671.867713525407</v>
       </c>
       <c r="O300">
         <v>267.002528924357</v>
@@ -22832,13 +22832,13 @@
         <v>3556.232816156792</v>
       </c>
       <c r="Q300">
-        <v>16.97415372359802</v>
+        <v>17.42814713167132</v>
       </c>
       <c r="R300">
-        <v>149.1964709406366</v>
+        <v>115.6348973686149</v>
       </c>
       <c r="S300">
-        <v>22.9897669355236</v>
+        <v>23.02548066137803</v>
       </c>
       <c r="T300">
         <v>153.6</v>
@@ -22847,10 +22847,10 @@
         <v>4380</v>
       </c>
       <c r="V300">
-        <v>0.06357300731187784</v>
+        <v>0.0652733410499224</v>
       </c>
       <c r="W300">
-        <v>0.04195351616542155</v>
+        <v>0.03251612122897542</v>
       </c>
       <c r="X300">
         <v>2030</v>
@@ -22888,16 +22888,16 @@
         <v>92</v>
       </c>
       <c r="K301">
-        <v>91530.91698707784</v>
+        <v>91555.83560616118</v>
       </c>
       <c r="L301">
-        <v>102.5990446473618</v>
+        <v>102.6939150718847</v>
       </c>
       <c r="M301">
-        <v>102.5990446473618</v>
+        <v>102.6939150718847</v>
       </c>
       <c r="N301">
-        <v>987.0204820224494</v>
+        <v>977.324029538358</v>
       </c>
       <c r="O301">
         <v>93.12047186834673</v>
@@ -22906,13 +22906,13 @@
         <v>930.7118012344204</v>
       </c>
       <c r="Q301">
-        <v>9.478572779015053</v>
+        <v>9.573443203538019</v>
       </c>
       <c r="R301">
-        <v>56.30868078802905</v>
+        <v>46.61222830393763</v>
       </c>
       <c r="S301">
-        <v>5.648609304480838</v>
+        <v>5.653061856090656</v>
       </c>
       <c r="T301">
         <v>415</v>
@@ -22921,10 +22921,10 @@
         <v>430</v>
       </c>
       <c r="V301">
-        <v>0.1017882812322495</v>
+        <v>0.1028070735839151</v>
       </c>
       <c r="W301">
-        <v>0.06050066273291668</v>
+        <v>0.05008234368804066</v>
       </c>
       <c r="X301">
         <v>2030</v>
@@ -22965,13 +22965,13 @@
         <v>38370</v>
       </c>
       <c r="L302">
-        <v>139.4634045133716</v>
+        <v>139.9032465339321</v>
       </c>
       <c r="M302">
-        <v>139.4634045133716</v>
+        <v>139.9032465339321</v>
       </c>
       <c r="N302">
-        <v>248.7119372834014</v>
+        <v>249.0682871352266</v>
       </c>
       <c r="O302">
         <v>147.751187510398</v>
@@ -22980,13 +22980,13 @@
         <v>259.5904230422387</v>
       </c>
       <c r="Q302">
-        <v>-8.287782997026397</v>
+        <v>-7.847940976465878</v>
       </c>
       <c r="R302">
-        <v>-10.87848575883731</v>
+        <v>-10.52213590701211</v>
       </c>
       <c r="S302">
-        <v>17.75550223521495</v>
+        <v>17.81149983549191</v>
       </c>
       <c r="T302">
         <v>483</v>
@@ -22995,10 +22995,10 @@
         <v>140</v>
       </c>
       <c r="V302">
-        <v>-0.05609283510119435</v>
+        <v>-0.05311592487819146</v>
       </c>
       <c r="W302">
-        <v>-0.04190634473856242</v>
+        <v>-0.04053360591542326</v>
       </c>
       <c r="X302">
         <v>2030</v>
@@ -23036,16 +23036,16 @@
         <v>91</v>
       </c>
       <c r="K303">
-        <v>35933.02392200158</v>
+        <v>35932.97899889841</v>
       </c>
       <c r="L303">
-        <v>712.4701047615389</v>
+        <v>715.1648923205197</v>
       </c>
       <c r="M303">
-        <v>712.4701047615389</v>
+        <v>715.1648923205197</v>
       </c>
       <c r="N303">
-        <v>1763.106895570103</v>
+        <v>1766.508951444358</v>
       </c>
       <c r="O303">
         <v>714.0428931425299</v>
@@ -23054,13 +23054,13 @@
         <v>1763.435835902707</v>
       </c>
       <c r="Q303">
-        <v>-1.572788380991028</v>
+        <v>1.121999177989778</v>
       </c>
       <c r="R303">
-        <v>-0.3289403326041338</v>
+        <v>3.073115541650623</v>
       </c>
       <c r="S303">
-        <v>101.254924195064</v>
+        <v>101.6380778169616</v>
       </c>
       <c r="T303">
         <v>2617.3</v>
@@ -23069,10 +23069,10 @@
         <v>1570</v>
       </c>
       <c r="V303">
-        <v>-0.002202652524233001</v>
+        <v>0.001571333023219119</v>
       </c>
       <c r="W303">
-        <v>-0.0001865337688545659</v>
+        <v>0.001742686339408253</v>
       </c>
       <c r="X303">
         <v>2030</v>
@@ -23110,16 +23110,16 @@
         <v>91</v>
       </c>
       <c r="K304">
-        <v>75965.8178952239</v>
+        <v>75956.2024844413</v>
       </c>
       <c r="L304">
-        <v>2455.971847913574</v>
+        <v>2465.032074936606</v>
       </c>
       <c r="M304">
-        <v>2455.971847913574</v>
+        <v>2465.032074936606</v>
       </c>
       <c r="N304">
-        <v>9863.507558945041</v>
+        <v>9851.891362096014</v>
       </c>
       <c r="O304">
         <v>2500.299605503861</v>
@@ -23128,13 +23128,13 @@
         <v>9950.779667838862</v>
       </c>
       <c r="Q304">
-        <v>-44.32775759028709</v>
+        <v>-35.26753056725465</v>
       </c>
       <c r="R304">
-        <v>-87.2721088938215</v>
+        <v>-98.88830574284839</v>
       </c>
       <c r="S304">
-        <v>215.2537983310042</v>
+        <v>216.050735950531</v>
       </c>
       <c r="T304">
         <v>2682.3</v>
@@ -23143,10 +23143,10 @@
         <v>9220</v>
       </c>
       <c r="V304">
-        <v>-0.01772897835631748</v>
+        <v>-0.01410532181408217</v>
       </c>
       <c r="W304">
-        <v>-0.00877037898606949</v>
+        <v>-0.009937744482722048</v>
       </c>
       <c r="X304">
         <v>2030</v>
@@ -23184,16 +23184,16 @@
         <v>91</v>
       </c>
       <c r="K305">
-        <v>48467.47649518823</v>
+        <v>48464.79776774956</v>
       </c>
       <c r="L305">
-        <v>9313.810501143464</v>
+        <v>9348.807889922411</v>
       </c>
       <c r="M305">
-        <v>9313.810501143464</v>
+        <v>9348.807889922411</v>
       </c>
       <c r="N305">
-        <v>26459.33399312237</v>
+        <v>26480.45393904094</v>
       </c>
       <c r="O305">
         <v>9786.902357083578</v>
@@ -23202,13 +23202,13 @@
         <v>27802.54411727167</v>
       </c>
       <c r="Q305">
-        <v>-473.0918559401143</v>
+        <v>-438.0944671611669</v>
       </c>
       <c r="R305">
-        <v>-1343.210124149307</v>
+        <v>-1322.090178230734</v>
       </c>
       <c r="S305">
-        <v>904.219542800266</v>
+        <v>907.6151320585482</v>
       </c>
       <c r="T305">
         <v>9674.400000000001</v>
@@ -23217,10 +23217,10 @@
         <v>28430</v>
       </c>
       <c r="V305">
-        <v>-0.04833928434952652</v>
+        <v>-0.0447633430044474</v>
       </c>
       <c r="W305">
-        <v>-0.04831248962266262</v>
+        <v>-0.04755284885635399</v>
       </c>
       <c r="X305">
         <v>2030</v>
@@ -23258,16 +23258,16 @@
         <v>91</v>
       </c>
       <c r="K306">
-        <v>62416.94918434384</v>
+        <v>62416.72594192659</v>
       </c>
       <c r="L306">
-        <v>4887.510428743544</v>
+        <v>4897.648684900449</v>
       </c>
       <c r="M306">
-        <v>4887.510428743544</v>
+        <v>4897.648684900449</v>
       </c>
       <c r="N306">
-        <v>7060.935786211747</v>
+        <v>7059.166735215379</v>
       </c>
       <c r="O306">
         <v>4528.691097083171</v>
@@ -23276,13 +23276,13 @@
         <v>6684.053473328399</v>
       </c>
       <c r="Q306">
-        <v>358.8193316603729</v>
+        <v>368.9575878172773</v>
       </c>
       <c r="R306">
-        <v>376.8823128833474</v>
+        <v>375.1132618869797</v>
       </c>
       <c r="S306">
-        <v>450.7334028501227</v>
+        <v>451.6701830383074</v>
       </c>
       <c r="T306">
         <v>960</v>
@@ -23291,10 +23291,10 @@
         <v>6340</v>
       </c>
       <c r="V306">
-        <v>0.07923245899714387</v>
+        <v>0.08147113148320374</v>
       </c>
       <c r="W306">
-        <v>0.0563852929045576</v>
+        <v>0.05612062551321688</v>
       </c>
       <c r="X306">
         <v>2030</v>
@@ -23332,16 +23332,16 @@
         <v>91</v>
       </c>
       <c r="K307">
-        <v>62250.02011679656</v>
+        <v>62248.44121530891</v>
       </c>
       <c r="L307">
-        <v>11595.17206098061</v>
+        <v>11630.91130090308</v>
       </c>
       <c r="M307">
-        <v>11595.17206098061</v>
+        <v>11630.91130090308</v>
       </c>
       <c r="N307">
-        <v>19399.98178686546</v>
+        <v>19457.55698159563</v>
       </c>
       <c r="O307">
         <v>10797.73359988231</v>
@@ -23350,13 +23350,13 @@
         <v>18366.84170045448</v>
       </c>
       <c r="Q307">
-        <v>797.4384610983052</v>
+        <v>833.1777010207697</v>
       </c>
       <c r="R307">
-        <v>1033.140086410986</v>
+        <v>1090.715281141147</v>
       </c>
       <c r="S307">
-        <v>1075.496495883546</v>
+        <v>1078.840021956802</v>
       </c>
       <c r="T307">
         <v>2231.1</v>
@@ -23365,10 +23365,10 @@
         <v>19550</v>
       </c>
       <c r="V307">
-        <v>0.07385239260829672</v>
+        <v>0.07716227607521742</v>
       </c>
       <c r="W307">
-        <v>0.05625028533813851</v>
+        <v>0.05938502105749394</v>
       </c>
       <c r="X307">
         <v>2030</v>
@@ -23406,16 +23406,16 @@
         <v>91</v>
       </c>
       <c r="K308">
-        <v>46485.23331598974</v>
+        <v>46487.15192979916</v>
       </c>
       <c r="L308">
-        <v>142526.7462263151</v>
+        <v>142943.0268952858</v>
       </c>
       <c r="M308">
-        <v>142526.7462263151</v>
+        <v>142943.0268952858</v>
       </c>
       <c r="N308">
-        <v>228344.3820657595</v>
+        <v>229101.5283195282</v>
       </c>
       <c r="O308">
         <v>140895.5563777906</v>
@@ -23424,13 +23424,13 @@
         <v>229819.6469961244</v>
       </c>
       <c r="Q308">
-        <v>1631.189848524547</v>
+        <v>2047.470517495181</v>
       </c>
       <c r="R308">
-        <v>-1475.264930364909</v>
+        <v>-718.1186765962048</v>
       </c>
       <c r="S308">
-        <v>14513.86706672405</v>
+        <v>14555.96663575679</v>
       </c>
       <c r="T308">
         <v>4161.800000000001</v>
@@ -23439,10 +23439,10 @@
         <v>227490</v>
       </c>
       <c r="V308">
-        <v>0.01157729803877387</v>
+        <v>0.01453183173502784</v>
       </c>
       <c r="W308">
-        <v>-0.00641922894603431</v>
+        <v>-0.003124705332996682</v>
       </c>
       <c r="X308">
         <v>2030</v>
@@ -23480,16 +23480,16 @@
         <v>91</v>
       </c>
       <c r="K309">
-        <v>42535.16634396883</v>
+        <v>42536.94853572476</v>
       </c>
       <c r="L309">
-        <v>11506.97501766831</v>
+        <v>11547.41845134334</v>
       </c>
       <c r="M309">
-        <v>11506.97501766831</v>
+        <v>11547.41845134334</v>
       </c>
       <c r="N309">
-        <v>20121.42887660769</v>
+        <v>20203.01494331548</v>
       </c>
       <c r="O309">
         <v>11556.97270728686</v>
@@ -23498,13 +23498,13 @@
         <v>20346.01390105237</v>
       </c>
       <c r="Q309">
-        <v>-49.99768961854716</v>
+        <v>-9.554255943514363</v>
       </c>
       <c r="R309">
-        <v>-224.5850244446847</v>
+        <v>-142.9989577368942</v>
       </c>
       <c r="S309">
-        <v>1368.350287530096</v>
+        <v>1373.141306718948</v>
       </c>
       <c r="T309">
         <v>9291.099999999999</v>
@@ -23513,10 +23513,10 @@
         <v>19570</v>
       </c>
       <c r="V309">
-        <v>-0.004326192583895504</v>
+        <v>-0.0008267092244226076</v>
       </c>
       <c r="W309">
-        <v>-0.01103828128383753</v>
+        <v>-0.007028352503460041</v>
       </c>
       <c r="X309">
         <v>2030</v>
